--- a/docs/Qhub - مصفوفة الباقات والمزايا.xlsx
+++ b/docs/Qhub - مصفوفة الباقات والمزايا.xlsx
@@ -82,6 +82,11 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="00CBD5E1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00166534"/>
       <sz val="11"/>
@@ -91,11 +96,6 @@
       <b val="1"/>
       <color rgb="00166534"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00CBD5E1"/>
-      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -236,11 +236,11 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1009,7 +1009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H86"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1253,50 +1253,54 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>الحدود والأساسيات</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>طلب اشتراك بحدود مخصّصة مع تتبّع حالة الطلب</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G10" s="19" t="inlineStr">
+        <is>
+          <t>✅ منفّذ</t>
+        </is>
+      </c>
+      <c r="H10" s="16" t="inlineStr">
+        <is>
+          <t>نموذج + طابور أدمن + تتبّع عند العميل: بانتظار الرد ← بانتظار الدفع ← تم الاشتراك</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>القنوات</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>القنوات</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>WhatsApp Business</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G11" s="18" t="inlineStr">
-        <is>
-          <t>✅ منفّذ</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="inlineStr"/>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
@@ -1306,39 +1310,35 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>ويدجت الموقع</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G12" s="18" t="inlineStr">
-        <is>
-          <t>✅ منفّذ</t>
-        </is>
-      </c>
-      <c r="H12" s="16" t="inlineStr">
-        <is>
-          <t>/channels/widget بإعدادات مستقلة</t>
-        </is>
-      </c>
+          <t>WhatsApp Business</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E12" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F12" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G12" s="19" t="inlineStr">
+        <is>
+          <t>✅ منفّذ</t>
+        </is>
+      </c>
+      <c r="H12" s="16" t="inlineStr"/>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
@@ -1348,35 +1348,39 @@
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>Instagram Direct</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>✅ منفّذ</t>
-        </is>
-      </c>
-      <c r="H13" s="16" t="inlineStr"/>
+          <t>ويدجت الموقع</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G13" s="19" t="inlineStr">
+        <is>
+          <t>✅ منفّذ</t>
+        </is>
+      </c>
+      <c r="H13" s="16" t="inlineStr">
+        <is>
+          <t>/channels/widget بإعدادات مستقلة</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
@@ -1386,30 +1390,30 @@
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>Facebook Messenger</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G14" s="18" t="inlineStr">
+          <t>Instagram Direct</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E14" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F14" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G14" s="19" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -1424,30 +1428,30 @@
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>Telegram</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G15" s="18" t="inlineStr">
+          <t>Facebook Messenger</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E15" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G15" s="19" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -1462,39 +1466,35 @@
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>البريد الإلكتروني</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>✅ منفّذ</t>
-        </is>
-      </c>
-      <c r="H16" s="16" t="inlineStr">
-        <is>
-          <t>النظام يدعم 5 أنواع: Gmail · Outlook · Yahoo · SMTP · email</t>
-        </is>
-      </c>
+          <t>Telegram</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E16" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F16" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G16" s="19" t="inlineStr">
+        <is>
+          <t>✅ منفّذ</t>
+        </is>
+      </c>
+      <c r="H16" s="16" t="inlineStr"/>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="12" t="inlineStr">
@@ -1504,35 +1504,39 @@
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>X (Twitter)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G17" s="18" t="inlineStr">
-        <is>
-          <t>✅ منفّذ</t>
-        </is>
-      </c>
-      <c r="H17" s="16" t="inlineStr"/>
+          <t>البريد الإلكتروني</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E17" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F17" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G17" s="19" t="inlineStr">
+        <is>
+          <t>✅ منفّذ</t>
+        </is>
+      </c>
+      <c r="H17" s="16" t="inlineStr">
+        <is>
+          <t>النظام يدعم 5 أنواع: Gmail · Outlook · Yahoo · SMTP · email</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
@@ -1542,30 +1546,30 @@
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>ربط سلة وزد</t>
-        </is>
-      </c>
-      <c r="C18" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F18" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G18" s="18" t="inlineStr">
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E18" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F18" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G18" s="19" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -1580,80 +1584,80 @@
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
+          <t>ربط سلة وزد</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E19" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F19" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G19" s="19" t="inlineStr">
+        <is>
+          <t>✅ منفّذ</t>
+        </is>
+      </c>
+      <c r="H19" s="16" t="inlineStr"/>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>القنوات</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
           <t>ربط Shopify و WooCommerce</t>
         </is>
       </c>
-      <c r="C19" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D19" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G19" s="18" t="inlineStr">
-        <is>
-          <t>✅ منفّذ</t>
-        </is>
-      </c>
-      <c r="H19" s="16" t="inlineStr"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E20" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F20" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G20" s="19" t="inlineStr">
+        <is>
+          <t>✅ منفّذ</t>
+        </is>
+      </c>
+      <c r="H20" s="16" t="inlineStr"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>صندوق الوارد الموحّد</t>
         </is>
       </c>
-    </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>صندوق الوارد الموحّد</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>صندوق وارد موحّد لكل القنوات</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G21" s="18" t="inlineStr">
-        <is>
-          <t>✅ منفّذ</t>
-        </is>
-      </c>
-      <c r="H21" s="16" t="inlineStr"/>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="12" t="inlineStr">
@@ -1663,39 +1667,35 @@
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>ملاحظات داخلية بين الفريق</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G22" s="18" t="inlineStr">
-        <is>
-          <t>✅ منفّذ</t>
-        </is>
-      </c>
-      <c r="H22" s="16" t="inlineStr">
-        <is>
-          <t>وضع «ملاحظة» في صندوق الكتابة</t>
-        </is>
-      </c>
+          <t>صندوق وارد موحّد لكل القنوات</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E22" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F22" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G22" s="19" t="inlineStr">
+        <is>
+          <t>✅ منفّذ</t>
+        </is>
+      </c>
+      <c r="H22" s="16" t="inlineStr"/>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="12" t="inlineStr">
@@ -1705,37 +1705,37 @@
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>الردود المحفوظة (Quick Replies)</t>
-        </is>
-      </c>
-      <c r="C23" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D23" s="14" t="inlineStr">
-        <is>
-          <t>بلا حد</t>
-        </is>
-      </c>
-      <c r="E23" s="14" t="inlineStr">
-        <is>
-          <t>بلا حد</t>
-        </is>
-      </c>
-      <c r="F23" s="14" t="inlineStr">
-        <is>
-          <t>بلا حد</t>
-        </is>
-      </c>
-      <c r="G23" s="18" t="inlineStr">
+          <t>ملاحظات داخلية بين الفريق</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D23" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E23" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F23" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G23" s="19" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
       </c>
       <c r="H23" s="16" t="inlineStr">
         <is>
-          <t>/saved-replies</t>
+          <t>وضع «ملاحظة» في صندوق الكتابة</t>
         </is>
       </c>
     </row>
@@ -1747,37 +1747,37 @@
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>الوسوم (Tags)</t>
+          <t>الردود المحفوظة (Quick Replies)</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G24" s="18" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>بلا حد</t>
+        </is>
+      </c>
+      <c r="E24" s="14" t="inlineStr">
+        <is>
+          <t>بلا حد</t>
+        </is>
+      </c>
+      <c r="F24" s="14" t="inlineStr">
+        <is>
+          <t>بلا حد</t>
+        </is>
+      </c>
+      <c r="G24" s="19" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
       </c>
       <c r="H24" s="16" t="inlineStr">
         <is>
-          <t>/tags</t>
+          <t>/saved-replies</t>
         </is>
       </c>
     </row>
@@ -1789,37 +1789,37 @@
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>الرسائل الصوتية — تسجيل وإرسال</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G25" s="18" t="inlineStr">
+          <t>الوسوم (Tags)</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E25" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F25" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G25" s="19" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
       </c>
       <c r="H25" s="16" t="inlineStr">
         <is>
-          <t>MediaRecorder حقيقي — غير مذكور في الملف السابق</t>
+          <t>/tags</t>
         </is>
       </c>
     </row>
@@ -1831,37 +1831,37 @@
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>تعديل الرسالة المُرسَلة خلال 30 دقيقة</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G26" s="18" t="inlineStr">
+          <t>الرسائل الصوتية — تسجيل وإرسال</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E26" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F26" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G26" s="19" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
       </c>
       <c r="H26" s="16" t="inlineStr">
         <is>
-          <t>غير مذكور في الملف السابق</t>
+          <t>MediaRecorder حقيقي — غير مذكور في الملف السابق</t>
         </is>
       </c>
     </row>
@@ -1873,30 +1873,30 @@
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>فهرسة دورات المحادثة داخل الثريد</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G27" s="18" t="inlineStr">
+          <t>تعديل الرسالة المُرسَلة خلال 30 دقيقة</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D27" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E27" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F27" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G27" s="19" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -1915,86 +1915,86 @@
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
+          <t>فهرسة دورات المحادثة داخل الثريد</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D28" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E28" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F28" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G28" s="19" t="inlineStr">
+        <is>
+          <t>✅ منفّذ</t>
+        </is>
+      </c>
+      <c r="H28" s="16" t="inlineStr">
+        <is>
+          <t>غير مذكور في الملف السابق</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>صندوق الوارد الموحّد</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
           <t>تطبيق هاتف للموظفين</t>
         </is>
       </c>
-      <c r="C28" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F28" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G28" s="20" t="inlineStr">
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D29" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E29" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F29" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G29" s="20" t="inlineStr">
         <is>
           <t>❌ غير منفّذ</t>
         </is>
       </c>
-      <c r="H28" s="16" t="inlineStr">
+      <c r="H29" s="16" t="inlineStr">
         <is>
           <t>لا وجود له في هذا الريبو إطلاقاً</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>الذكاء الاصطناعي</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>الذكاء الاصطناعي</t>
-        </is>
-      </c>
-      <c r="B30" s="13" t="inlineStr">
-        <is>
-          <t>رصيد ردود AI شهرياً</t>
-        </is>
-      </c>
-      <c r="C30" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D30" s="14" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
-      </c>
-      <c r="E30" s="14" t="inlineStr">
-        <is>
-          <t>10,000</t>
-        </is>
-      </c>
-      <c r="F30" s="14" t="inlineStr">
-        <is>
-          <t>مخصّص</t>
-        </is>
-      </c>
-      <c r="G30" s="15" t="inlineStr">
-        <is>
-          <t>⚠️ جزئي</t>
-        </is>
-      </c>
-      <c r="H30" s="16" t="inlineStr">
-        <is>
-          <t>رصيد عام في إعدادات AI — غير مربوط بالباقة</t>
         </is>
       </c>
     </row>
@@ -2006,27 +2006,27 @@
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>ردود تلقائية ذكية 24/7</t>
-        </is>
-      </c>
-      <c r="C31" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F31" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
+          <t>رصيد ردود AI شهرياً</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>مخصّص</t>
         </is>
       </c>
       <c r="G31" s="15" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="H31" s="16" t="inlineStr">
         <is>
-          <t>getAIResponse في utils/ai.ts دالة وهمية</t>
+          <t>رصيد عام في إعدادات AI — غير مربوط بالباقة</t>
         </is>
       </c>
     </row>
@@ -2048,37 +2048,37 @@
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>فهم اللهجات العربية</t>
-        </is>
-      </c>
-      <c r="C32" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E32" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F32" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G32" s="18" t="inlineStr">
-        <is>
-          <t>✅ منفّذ</t>
+          <t>ردود تلقائية ذكية 24/7</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D32" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E32" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F32" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G32" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ جزئي</t>
         </is>
       </c>
       <c r="H32" s="16" t="inlineStr">
         <is>
-          <t>dialect + gulfCountry</t>
+          <t>getAIResponse في utils/ai.ts دالة وهمية</t>
         </is>
       </c>
     </row>
@@ -2090,37 +2090,37 @@
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>تحويل تلقائي للموظف + ملخّص</t>
-        </is>
-      </c>
-      <c r="C33" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D33" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E33" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F33" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G33" s="18" t="inlineStr">
+          <t>فهم اللهجات العربية</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D33" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E33" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F33" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G33" s="19" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
       </c>
       <c r="H33" s="16" t="inlineStr">
         <is>
-          <t>transferOn* — ستّة محفّزات</t>
+          <t>dialect + gulfCountry</t>
         </is>
       </c>
     </row>
@@ -2132,37 +2132,37 @@
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>تزويد المساعد الذكي بالمستندات</t>
-        </is>
-      </c>
-      <c r="C34" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D34" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E34" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F34" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G34" s="18" t="inlineStr">
+          <t>تحويل تلقائي للموظف + ملخّص</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D34" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E34" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F34" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G34" s="19" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
       </c>
       <c r="H34" s="16" t="inlineStr">
         <is>
-          <t>useKnowledgeBase</t>
+          <t>transferOn* — ستّة محفّزات</t>
         </is>
       </c>
     </row>
@@ -2174,37 +2174,37 @@
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>قاعدة معلومات خاصة بالنظام</t>
-        </is>
-      </c>
-      <c r="C35" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D35" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E35" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F35" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G35" s="18" t="inlineStr">
+          <t>تزويد المساعد الذكي بالمستندات</t>
+        </is>
+      </c>
+      <c r="C35" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D35" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E35" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F35" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G35" s="19" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
       </c>
       <c r="H35" s="16" t="inlineStr">
         <is>
-          <t>/knowledge-base</t>
+          <t>useKnowledgeBase</t>
         </is>
       </c>
     </row>
@@ -2216,37 +2216,37 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>استثناء مواضيع حسّاسة</t>
-        </is>
-      </c>
-      <c r="C36" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D36" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E36" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F36" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G36" s="18" t="inlineStr">
+          <t>قاعدة معلومات خاصة بالنظام</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D36" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E36" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F36" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G36" s="19" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
       </c>
       <c r="H36" s="16" t="inlineStr">
         <is>
-          <t>forbiddenTopics + forbiddenReply</t>
+          <t>/knowledge-base</t>
         </is>
       </c>
     </row>
@@ -2258,37 +2258,37 @@
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>تحويل فوري بكلمة مفتاحية</t>
-        </is>
-      </c>
-      <c r="C37" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D37" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E37" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F37" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G37" s="18" t="inlineStr">
+          <t>استثناء مواضيع حسّاسة</t>
+        </is>
+      </c>
+      <c r="C37" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D37" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E37" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F37" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G37" s="19" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
       </c>
       <c r="H37" s="16" t="inlineStr">
         <is>
-          <t>transferKeywords</t>
+          <t>forbiddenTopics + forbiddenReply</t>
         </is>
       </c>
     </row>
@@ -2300,37 +2300,37 @@
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>إعدادات AI منفصلة لكل قناة</t>
-        </is>
-      </c>
-      <c r="C38" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D38" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E38" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F38" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G38" s="18" t="inlineStr">
+          <t>تحويل فوري بكلمة مفتاحية</t>
+        </is>
+      </c>
+      <c r="C38" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D38" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E38" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F38" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G38" s="19" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
       </c>
       <c r="H38" s="16" t="inlineStr">
         <is>
-          <t>channelBehaviors</t>
+          <t>transferKeywords</t>
         </is>
       </c>
     </row>
@@ -2342,37 +2342,37 @@
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>تفريغ الرسائل الصوتية</t>
-        </is>
-      </c>
-      <c r="C39" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D39" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E39" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F39" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G39" s="15" t="inlineStr">
-        <is>
-          <t>⚠️ جزئي</t>
+          <t>إعدادات AI منفصلة لكل قناة</t>
+        </is>
+      </c>
+      <c r="C39" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D39" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E39" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F39" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G39" s="19" t="inlineStr">
+        <is>
+          <t>✅ منفّذ</t>
         </is>
       </c>
       <c r="H39" s="16" t="inlineStr">
         <is>
-          <t>الواجهة كاملة — transcribeAudio دالة وهمية ولا شيء يُشغّلها</t>
+          <t>channelBehaviors</t>
         </is>
       </c>
     </row>
@@ -2384,25 +2384,25 @@
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>التعلّم من أرشيف المحادثات</t>
-        </is>
-      </c>
-      <c r="C40" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D40" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E40" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F40" s="17" t="inlineStr">
+          <t>تفريغ الرسائل الصوتية</t>
+        </is>
+      </c>
+      <c r="C40" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D40" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E40" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F40" s="18" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="H40" s="16" t="inlineStr">
         <is>
-          <t>مفتاح learnFromAgents بلا منطق خلفه</t>
+          <t>الواجهة كاملة — transcribeAudio دالة وهمية ولا شيء يُشغّلها</t>
         </is>
       </c>
     </row>
@@ -2426,25 +2426,25 @@
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>تحليل الصور والفيديو وملفات PDF</t>
-        </is>
-      </c>
-      <c r="C41" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D41" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E41" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F41" s="17" t="inlineStr">
+          <t>التعلّم من أرشيف المحادثات</t>
+        </is>
+      </c>
+      <c r="C41" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D41" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E41" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F41" s="18" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="H41" s="16" t="inlineStr">
         <is>
-          <t>مفاتيح في الإعدادات بلا منطق — غير مذكورة في الملف السابق</t>
+          <t>مفتاح learnFromAgents بلا منطق خلفه</t>
         </is>
       </c>
     </row>
@@ -2468,25 +2468,25 @@
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>تحليل مشاعر العميل</t>
-        </is>
-      </c>
-      <c r="C42" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D42" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E42" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F42" s="17" t="inlineStr">
+          <t>تحليل الصور والفيديو وملفات PDF</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D42" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E42" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F42" s="18" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="H42" s="16" t="inlineStr">
         <is>
-          <t>sentimentAnalysis — مفتاح بلا منطق</t>
+          <t>مفاتيح في الإعدادات بلا منطق — غير مذكورة في الملف السابق</t>
         </is>
       </c>
     </row>
@@ -2510,86 +2510,86 @@
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
+          <t>تحليل مشاعر العميل</t>
+        </is>
+      </c>
+      <c r="C43" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D43" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E43" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F43" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G43" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ جزئي</t>
+        </is>
+      </c>
+      <c r="H43" s="16" t="inlineStr">
+        <is>
+          <t>sentimentAnalysis — مفتاح بلا منطق</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>الذكاء الاصطناعي</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
           <t>اقتراحات ذكية للردّ</t>
         </is>
       </c>
-      <c r="C43" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D43" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E43" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F43" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G43" s="15" t="inlineStr">
+      <c r="C44" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D44" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E44" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F44" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G44" s="15" t="inlineStr">
         <is>
           <t>⚠️ جزئي</t>
         </is>
       </c>
-      <c r="H43" s="16" t="inlineStr">
+      <c r="H44" s="16" t="inlineStr">
         <is>
           <t>smartSuggestions — مفتاح بلا منطق</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="11" t="inlineStr">
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>إدارة الفريق والصلاحيات</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="24" customHeight="1">
-      <c r="A45" s="12" t="inlineStr">
-        <is>
-          <t>إدارة الفريق والصلاحيات</t>
-        </is>
-      </c>
-      <c r="B45" s="13" t="inlineStr">
-        <is>
-          <t>أدوار الموظفين والصلاحيات</t>
-        </is>
-      </c>
-      <c r="C45" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D45" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E45" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F45" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G45" s="18" t="inlineStr">
-        <is>
-          <t>✅ منفّذ</t>
-        </is>
-      </c>
-      <c r="H45" s="16" t="inlineStr">
-        <is>
-          <t>/team/roles</t>
         </is>
       </c>
     </row>
@@ -2601,37 +2601,37 @@
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>الأقسام مع هدف زمن استجابة</t>
-        </is>
-      </c>
-      <c r="C46" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D46" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E46" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F46" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G46" s="18" t="inlineStr">
+          <t>أدوار الموظفين والصلاحيات</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D46" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E46" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F46" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G46" s="19" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
       </c>
       <c r="H46" s="16" t="inlineStr">
         <is>
-          <t>slaMinutes — غير مذكور في الملف السابق</t>
+          <t>/team/roles</t>
         </is>
       </c>
     </row>
@@ -2643,37 +2643,37 @@
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>رد تلقائي خارج الدوام</t>
-        </is>
-      </c>
-      <c r="C47" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D47" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E47" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F47" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G47" s="18" t="inlineStr">
+          <t>الأقسام مع هدف زمن استجابة</t>
+        </is>
+      </c>
+      <c r="C47" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D47" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E47" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F47" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G47" s="19" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
       </c>
       <c r="H47" s="16" t="inlineStr">
         <is>
-          <t>alwaysOn + schedule + offHoursMessage</t>
+          <t>slaMinutes — غير مذكور في الملف السابق</t>
         </is>
       </c>
     </row>
@@ -2685,37 +2685,37 @@
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>حالة متاح/مشغول</t>
-        </is>
-      </c>
-      <c r="C48" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D48" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E48" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F48" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G48" s="18" t="inlineStr">
+          <t>رد تلقائي خارج الدوام</t>
+        </is>
+      </c>
+      <c r="C48" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D48" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E48" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F48" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G48" s="19" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
       </c>
       <c r="H48" s="16" t="inlineStr">
         <is>
-          <t>أُضيفت في جلسة 15 سبتمبر</t>
+          <t>alwaysOn + schedule + offHoursMessage</t>
         </is>
       </c>
     </row>
@@ -2727,37 +2727,37 @@
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>قواعد توزيع بكلمة مفتاحية</t>
-        </is>
-      </c>
-      <c r="C49" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D49" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E49" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F49" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G49" s="15" t="inlineStr">
-        <is>
-          <t>⚠️ جزئي</t>
+          <t>حالة متاح/مشغول</t>
+        </is>
+      </c>
+      <c r="C49" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D49" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E49" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F49" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G49" s="19" t="inlineStr">
+        <is>
+          <t>✅ منفّذ</t>
         </is>
       </c>
       <c r="H49" s="16" t="inlineStr">
         <is>
-          <t>routingKeywords يُحفظ ويُعدَّل — لا كود يقرأه</t>
+          <t>أُضيفت في جلسة 15 سبتمبر</t>
         </is>
       </c>
     </row>
@@ -2769,25 +2769,25 @@
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>سجلّ إجراءات الموظفين</t>
-        </is>
-      </c>
-      <c r="C50" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D50" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E50" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F50" s="17" t="inlineStr">
+          <t>قواعد توزيع بكلمة مفتاحية</t>
+        </is>
+      </c>
+      <c r="C50" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D50" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E50" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F50" s="18" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="H50" s="16" t="inlineStr">
         <is>
-          <t>السجل على مستوى المحادثة لا الموظف</t>
+          <t>routingKeywords يُحفظ ويُعدَّل — لا كود يقرأه</t>
         </is>
       </c>
     </row>
@@ -2811,122 +2811,130 @@
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
+          <t>سجلّ إجراءات الموظفين</t>
+        </is>
+      </c>
+      <c r="C51" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D51" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E51" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F51" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G51" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ جزئي</t>
+        </is>
+      </c>
+      <c r="H51" s="16" t="inlineStr">
+        <is>
+          <t>السجل على مستوى المحادثة لا الموظف</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="24" customHeight="1">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>إدارة الفريق والصلاحيات</t>
+        </is>
+      </c>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
           <t>توزيع تلقائي متوازن</t>
         </is>
       </c>
-      <c r="C51" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D51" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E51" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F51" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G51" s="20" t="inlineStr">
+      <c r="C52" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D52" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E52" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F52" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G52" s="20" t="inlineStr">
         <is>
           <t>❌ غير منفّذ</t>
         </is>
       </c>
-      <c r="H51" s="16" t="inlineStr">
+      <c r="H52" s="16" t="inlineStr">
         <is>
           <t>الإسناد يدوي بالكامل — لا round-robin</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="11" t="inlineStr">
-        <is>
-          <t>التسويق والحملات</t>
         </is>
       </c>
     </row>
     <row r="53" ht="24" customHeight="1">
       <c r="A53" s="12" t="inlineStr">
         <is>
+          <t>إدارة الفريق والصلاحيات</t>
+        </is>
+      </c>
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>التحقق بخطوتين (2FA) لحسابات الفريق</t>
+        </is>
+      </c>
+      <c r="C53" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D53" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E53" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F53" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G53" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ جزئي</t>
+        </is>
+      </c>
+      <c r="H53" s="16" t="inlineStr">
+        <is>
+          <t>يعمل في المتصفح بسرّ مشترك — غير آمن للإنتاج</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
           <t>التسويق والحملات</t>
         </is>
       </c>
-      <c r="B53" s="13" t="inlineStr">
-        <is>
-          <t>حملات واتساب</t>
-        </is>
-      </c>
-      <c r="C53" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D53" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E53" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F53" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G53" s="18" t="inlineStr">
-        <is>
-          <t>✅ منفّذ</t>
-        </is>
-      </c>
-      <c r="H53" s="16" t="inlineStr"/>
-    </row>
-    <row r="54" ht="24" customHeight="1">
-      <c r="A54" s="12" t="inlineStr">
-        <is>
-          <t>التسويق والحملات</t>
-        </is>
-      </c>
-      <c r="B54" s="13" t="inlineStr">
-        <is>
-          <t>حملات بريد إلكتروني</t>
-        </is>
-      </c>
-      <c r="C54" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D54" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E54" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F54" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G54" s="18" t="inlineStr">
-        <is>
-          <t>✅ منفّذ</t>
-        </is>
-      </c>
-      <c r="H54" s="16" t="inlineStr"/>
     </row>
     <row r="55" ht="24" customHeight="1">
       <c r="A55" s="12" t="inlineStr">
@@ -2936,39 +2944,35 @@
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>قوالب جاهزة</t>
-        </is>
-      </c>
-      <c r="C55" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D55" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E55" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F55" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G55" s="18" t="inlineStr">
-        <is>
-          <t>✅ منفّذ</t>
-        </is>
-      </c>
-      <c r="H55" s="16" t="inlineStr">
-        <is>
-          <t>/campaigns/templates</t>
-        </is>
-      </c>
+          <t>حملات واتساب</t>
+        </is>
+      </c>
+      <c r="C55" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D55" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E55" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F55" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G55" s="19" t="inlineStr">
+        <is>
+          <t>✅ منفّذ</t>
+        </is>
+      </c>
+      <c r="H55" s="16" t="inlineStr"/>
     </row>
     <row r="56" ht="24" customHeight="1">
       <c r="A56" s="12" t="inlineStr">
@@ -2978,30 +2982,30 @@
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
-          <t>تقسيم الجمهور بالوسوم</t>
-        </is>
-      </c>
-      <c r="C56" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D56" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E56" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F56" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G56" s="18" t="inlineStr">
+          <t>حملات بريد إلكتروني</t>
+        </is>
+      </c>
+      <c r="C56" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D56" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E56" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F56" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G56" s="19" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -3016,37 +3020,37 @@
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
-          <t>تقارير الحملات (وصلت/فُتحت/ردّوا)</t>
-        </is>
-      </c>
-      <c r="C57" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D57" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E57" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F57" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G57" s="18" t="inlineStr">
+          <t>قوالب جاهزة</t>
+        </is>
+      </c>
+      <c r="C57" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D57" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E57" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F57" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G57" s="19" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
       </c>
       <c r="H57" s="16" t="inlineStr">
         <is>
-          <t>openRate + تصدير CSV</t>
+          <t>/campaigns/templates</t>
         </is>
       </c>
     </row>
@@ -3058,39 +3062,35 @@
       </c>
       <c r="B58" s="13" t="inlineStr">
         <is>
-          <t>جدولة الإرسال</t>
-        </is>
-      </c>
-      <c r="C58" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D58" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E58" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F58" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G58" s="18" t="inlineStr">
-        <is>
-          <t>✅ منفّذ</t>
-        </is>
-      </c>
-      <c r="H58" s="16" t="inlineStr">
-        <is>
-          <t>scheduledAt</t>
-        </is>
-      </c>
+          <t>تقسيم الجمهور بالوسوم</t>
+        </is>
+      </c>
+      <c r="C58" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D58" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E58" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F58" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G58" s="19" t="inlineStr">
+        <is>
+          <t>✅ منفّذ</t>
+        </is>
+      </c>
+      <c r="H58" s="16" t="inlineStr"/>
     </row>
     <row r="59" ht="24" customHeight="1">
       <c r="A59" s="12" t="inlineStr">
@@ -3100,37 +3100,37 @@
       </c>
       <c r="B59" s="13" t="inlineStr">
         <is>
-          <t>رسائل حملات شهرياً</t>
-        </is>
-      </c>
-      <c r="C59" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D59" s="14" t="inlineStr">
-        <is>
-          <t>1,000</t>
-        </is>
-      </c>
-      <c r="E59" s="14" t="inlineStr">
-        <is>
-          <t>10,000</t>
-        </is>
-      </c>
-      <c r="F59" s="14" t="inlineStr">
-        <is>
-          <t>مخصّص</t>
-        </is>
-      </c>
-      <c r="G59" s="20" t="inlineStr">
-        <is>
-          <t>❌ غير منفّذ</t>
+          <t>تقارير الحملات (وصلت/فُتحت/ردّوا)</t>
+        </is>
+      </c>
+      <c r="C59" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D59" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E59" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F59" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G59" s="19" t="inlineStr">
+        <is>
+          <t>✅ منفّذ</t>
         </is>
       </c>
       <c r="H59" s="16" t="inlineStr">
         <is>
-          <t>لا حقل حصّة على الباقة — رسوم Meta منفصلة</t>
+          <t>openRate + تصدير CSV</t>
         </is>
       </c>
     </row>
@@ -3142,122 +3142,130 @@
       </c>
       <c r="B60" s="13" t="inlineStr">
         <is>
-          <t>إرسال تدريجي (حماية الرقم)</t>
-        </is>
-      </c>
-      <c r="C60" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D60" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E60" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F60" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G60" s="20" t="inlineStr">
+          <t>جدولة الإرسال</t>
+        </is>
+      </c>
+      <c r="C60" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D60" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E60" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F60" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G60" s="19" t="inlineStr">
+        <is>
+          <t>✅ منفّذ</t>
+        </is>
+      </c>
+      <c r="H60" s="16" t="inlineStr">
+        <is>
+          <t>scheduledAt</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="24" customHeight="1">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>التسويق والحملات</t>
+        </is>
+      </c>
+      <c r="B61" s="13" t="inlineStr">
+        <is>
+          <t>رسائل حملات شهرياً</t>
+        </is>
+      </c>
+      <c r="C61" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D61" s="14" t="inlineStr">
+        <is>
+          <t>1,000</t>
+        </is>
+      </c>
+      <c r="E61" s="14" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="F61" s="14" t="inlineStr">
+        <is>
+          <t>مخصّص</t>
+        </is>
+      </c>
+      <c r="G61" s="20" t="inlineStr">
         <is>
           <t>❌ غير منفّذ</t>
         </is>
       </c>
-      <c r="H60" s="16" t="inlineStr">
-        <is>
-          <t>لا وجود له</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="11" t="inlineStr">
-        <is>
-          <t>العملاء والدعم والتقارير</t>
+      <c r="H61" s="16" t="inlineStr">
+        <is>
+          <t>لا حقل حصّة على الباقة — رسوم Meta منفصلة</t>
         </is>
       </c>
     </row>
     <row r="62" ht="24" customHeight="1">
       <c r="A62" s="12" t="inlineStr">
         <is>
+          <t>التسويق والحملات</t>
+        </is>
+      </c>
+      <c r="B62" s="13" t="inlineStr">
+        <is>
+          <t>إرسال تدريجي (حماية الرقم)</t>
+        </is>
+      </c>
+      <c r="C62" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D62" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E62" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F62" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G62" s="20" t="inlineStr">
+        <is>
+          <t>❌ غير منفّذ</t>
+        </is>
+      </c>
+      <c r="H62" s="16" t="inlineStr">
+        <is>
+          <t>لا وجود له</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
           <t>العملاء والدعم والتقارير</t>
         </is>
       </c>
-      <c r="B62" s="13" t="inlineStr">
-        <is>
-          <t>ملف العميل وسجل تفاعلاته</t>
-        </is>
-      </c>
-      <c r="C62" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D62" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E62" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F62" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G62" s="18" t="inlineStr">
-        <is>
-          <t>✅ منفّذ</t>
-        </is>
-      </c>
-      <c r="H62" s="16" t="inlineStr"/>
-    </row>
-    <row r="63" ht="24" customHeight="1">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t>العملاء والدعم والتقارير</t>
-        </is>
-      </c>
-      <c r="B63" s="13" t="inlineStr">
-        <is>
-          <t>قاعدة المعرفة (Knowledge Base)</t>
-        </is>
-      </c>
-      <c r="C63" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D63" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E63" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F63" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G63" s="18" t="inlineStr">
-        <is>
-          <t>✅ منفّذ</t>
-        </is>
-      </c>
-      <c r="H63" s="16" t="inlineStr"/>
     </row>
     <row r="64" ht="24" customHeight="1">
       <c r="A64" s="12" t="inlineStr">
@@ -3267,30 +3275,30 @@
       </c>
       <c r="B64" s="13" t="inlineStr">
         <is>
-          <t>تصنيفات العملاء</t>
-        </is>
-      </c>
-      <c r="C64" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D64" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E64" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F64" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G64" s="18" t="inlineStr">
+          <t>ملف العميل وسجل تفاعلاته</t>
+        </is>
+      </c>
+      <c r="C64" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D64" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E64" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F64" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G64" s="19" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -3305,39 +3313,35 @@
       </c>
       <c r="B65" s="13" t="inlineStr">
         <is>
-          <t>تقارير أساسية (لوحة ملخّص)</t>
-        </is>
-      </c>
-      <c r="C65" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D65" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E65" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F65" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G65" s="18" t="inlineStr">
-        <is>
-          <t>✅ منفّذ</t>
-        </is>
-      </c>
-      <c r="H65" s="16" t="inlineStr">
-        <is>
-          <t>/overview</t>
-        </is>
-      </c>
+          <t>قاعدة المعرفة (Knowledge Base)</t>
+        </is>
+      </c>
+      <c r="C65" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D65" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E65" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F65" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G65" s="19" t="inlineStr">
+        <is>
+          <t>✅ منفّذ</t>
+        </is>
+      </c>
+      <c r="H65" s="16" t="inlineStr"/>
     </row>
     <row r="66" ht="24" customHeight="1">
       <c r="A66" s="12" t="inlineStr">
@@ -3347,39 +3351,35 @@
       </c>
       <c r="B66" s="13" t="inlineStr">
         <is>
-          <t>متوسط زمن أول ردّ</t>
-        </is>
-      </c>
-      <c r="C66" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D66" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E66" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F66" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G66" s="18" t="inlineStr">
-        <is>
-          <t>✅ منفّذ</t>
-        </is>
-      </c>
-      <c r="H66" s="16" t="inlineStr">
-        <is>
-          <t>Overview.tsx — avgResponse</t>
-        </is>
-      </c>
+          <t>تصنيفات العملاء</t>
+        </is>
+      </c>
+      <c r="C66" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D66" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E66" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F66" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G66" s="19" t="inlineStr">
+        <is>
+          <t>✅ منفّذ</t>
+        </is>
+      </c>
+      <c r="H66" s="16" t="inlineStr"/>
     </row>
     <row r="67" ht="24" customHeight="1">
       <c r="A67" s="12" t="inlineStr">
@@ -3389,37 +3389,37 @@
       </c>
       <c r="B67" s="13" t="inlineStr">
         <is>
-          <t>الشكاوى والاقتراحات</t>
-        </is>
-      </c>
-      <c r="C67" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D67" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E67" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F67" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G67" s="18" t="inlineStr">
+          <t>تقارير أساسية (لوحة ملخّص)</t>
+        </is>
+      </c>
+      <c r="C67" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D67" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E67" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F67" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G67" s="19" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
       </c>
       <c r="H67" s="16" t="inlineStr">
         <is>
-          <t>/feedback</t>
+          <t>/overview</t>
         </is>
       </c>
     </row>
@@ -3431,37 +3431,37 @@
       </c>
       <c r="B68" s="13" t="inlineStr">
         <is>
-          <t>تقييمات العملاء بعد المحادثة</t>
-        </is>
-      </c>
-      <c r="C68" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D68" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E68" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F68" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G68" s="18" t="inlineStr">
+          <t>متوسط زمن أول ردّ</t>
+        </is>
+      </c>
+      <c r="C68" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D68" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E68" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F68" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G68" s="19" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
       </c>
       <c r="H68" s="16" t="inlineStr">
         <is>
-          <t>/rating + صفحة تقييم عامة بتوكن</t>
+          <t>Overview.tsx — avgResponse</t>
         </is>
       </c>
     </row>
@@ -3473,37 +3473,37 @@
       </c>
       <c r="B69" s="13" t="inlineStr">
         <is>
-          <t>ساعات الذروة</t>
-        </is>
-      </c>
-      <c r="C69" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D69" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E69" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F69" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G69" s="18" t="inlineStr">
+          <t>الشكاوى والاقتراحات</t>
+        </is>
+      </c>
+      <c r="C69" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D69" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E69" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F69" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G69" s="19" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
       </c>
       <c r="H69" s="16" t="inlineStr">
         <is>
-          <t>Reports.tsx — خريطة حرارية</t>
+          <t>/feedback</t>
         </is>
       </c>
     </row>
@@ -3515,37 +3515,37 @@
       </c>
       <c r="B70" s="13" t="inlineStr">
         <is>
-          <t>سجل نشاط العميل</t>
-        </is>
-      </c>
-      <c r="C70" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D70" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F70" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G70" s="18" t="inlineStr">
+          <t>تقييمات العملاء بعد المحادثة</t>
+        </is>
+      </c>
+      <c r="C70" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D70" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E70" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F70" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G70" s="19" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
       </c>
       <c r="H70" s="16" t="inlineStr">
         <is>
-          <t>Contact.activityLog</t>
+          <t>/rating + صفحة تقييم عامة بتوكن</t>
         </is>
       </c>
     </row>
@@ -3557,600 +3557,172 @@
       </c>
       <c r="B71" s="13" t="inlineStr">
         <is>
-          <t>تنبيه عند تجاوز حد زمن الرد</t>
-        </is>
-      </c>
-      <c r="C71" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D71" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F71" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G71" s="15" t="inlineStr">
-        <is>
-          <t>⚠️ جزئي</t>
+          <t>ساعات الذروة</t>
+        </is>
+      </c>
+      <c r="C71" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D71" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E71" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F71" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G71" s="19" t="inlineStr">
+        <is>
+          <t>✅ منفّذ</t>
         </is>
       </c>
       <c r="H71" s="16" t="inlineStr">
         <is>
-          <t>الحد يُضبط على القسم — لا تنبيه يُطلَق</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="22" customHeight="1">
-      <c r="A72" s="11" t="inlineStr">
-        <is>
-          <t>الفوترة والاشتراك — مجموعة جديدة</t>
+          <t>Reports.tsx — خريطة حرارية</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="24" customHeight="1">
+      <c r="A72" s="12" t="inlineStr">
+        <is>
+          <t>العملاء والدعم والتقارير</t>
+        </is>
+      </c>
+      <c r="B72" s="13" t="inlineStr">
+        <is>
+          <t>سجل نشاط العميل</t>
+        </is>
+      </c>
+      <c r="C72" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D72" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F72" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G72" s="19" t="inlineStr">
+        <is>
+          <t>✅ منفّذ</t>
+        </is>
+      </c>
+      <c r="H72" s="16" t="inlineStr">
+        <is>
+          <t>Contact.activityLog</t>
         </is>
       </c>
     </row>
     <row r="73" ht="24" customHeight="1">
       <c r="A73" s="12" t="inlineStr">
         <is>
-          <t>الفوترة والاشتراك — مجموعة جديدة</t>
+          <t>العملاء والدعم والتقارير</t>
         </is>
       </c>
       <c r="B73" s="13" t="inlineStr">
         <is>
-          <t>الاشتراك وتغيير الباقة</t>
+          <t>تنبيه عند تجاوز حد زمن الرد</t>
         </is>
       </c>
       <c r="C73" s="17" t="inlineStr">
         <is>
-          <t>✔</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D73" s="17" t="inlineStr">
         <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E73" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F73" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G73" s="18" t="inlineStr">
-        <is>
-          <t>✅ منفّذ</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F73" s="18" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G73" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ جزئي</t>
         </is>
       </c>
       <c r="H73" s="16" t="inlineStr">
         <is>
-          <t>/subscribe</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="24" customHeight="1">
-      <c r="A74" s="12" t="inlineStr">
-        <is>
-          <t>الفوترة والاشتراك — مجموعة جديدة</t>
-        </is>
-      </c>
-      <c r="B74" s="13" t="inlineStr">
-        <is>
-          <t>الفواتير وتحميلها PDF</t>
-        </is>
-      </c>
-      <c r="C74" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D74" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E74" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F74" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G74" s="18" t="inlineStr">
-        <is>
-          <t>✅ منفّذ</t>
-        </is>
-      </c>
-      <c r="H74" s="16" t="inlineStr">
-        <is>
-          <t>/billing</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="24" customHeight="1">
-      <c r="A75" s="12" t="inlineStr">
-        <is>
-          <t>الفوترة والاشتراك — مجموعة جديدة</t>
-        </is>
-      </c>
-      <c r="B75" s="13" t="inlineStr">
-        <is>
-          <t>تخفيض مؤجّل لنهاية الدورة</t>
-        </is>
-      </c>
-      <c r="C75" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D75" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E75" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F75" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G75" s="18" t="inlineStr">
-        <is>
-          <t>✅ منفّذ</t>
-        </is>
-      </c>
-      <c r="H75" s="16" t="inlineStr">
-        <is>
-          <t>scheduledChange</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="24" customHeight="1">
-      <c r="A76" s="12" t="inlineStr">
-        <is>
-          <t>الفوترة والاشتراك — مجموعة جديدة</t>
-        </is>
-      </c>
-      <c r="B76" s="13" t="inlineStr">
-        <is>
-          <t>طلب اشتراك باقة المؤسسات</t>
-        </is>
-      </c>
-      <c r="C76" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D76" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E76" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F76" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G76" s="18" t="inlineStr">
-        <is>
-          <t>✅ منفّذ</t>
-        </is>
-      </c>
-      <c r="H76" s="16" t="inlineStr">
-        <is>
-          <t>نموذج + طابور أدمن</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="24" customHeight="1">
-      <c r="A77" s="12" t="inlineStr">
-        <is>
-          <t>الفوترة والاشتراك — مجموعة جديدة</t>
-        </is>
-      </c>
-      <c r="B77" s="13" t="inlineStr">
-        <is>
-          <t>تتبّع الطلب عند العميل</t>
-        </is>
-      </c>
-      <c r="C77" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D77" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E77" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F77" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G77" s="18" t="inlineStr">
-        <is>
-          <t>✅ منفّذ</t>
-        </is>
-      </c>
-      <c r="H77" s="16" t="inlineStr">
-        <is>
-          <t>بانتظار الرد ← بانتظار الدفع ← تم الاشتراك</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="24" customHeight="1">
-      <c r="A78" s="12" t="inlineStr">
-        <is>
-          <t>الفوترة والاشتراك — مجموعة جديدة</t>
-        </is>
-      </c>
-      <c r="B78" s="13" t="inlineStr">
-        <is>
-          <t>بوابة دفع Paymob</t>
-        </is>
-      </c>
-      <c r="C78" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D78" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E78" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F78" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G78" s="15" t="inlineStr">
-        <is>
-          <t>⚠️ جزئي</t>
-        </is>
-      </c>
-      <c r="H78" s="16" t="inlineStr">
-        <is>
-          <t>إعدادات ومفاتيح فقط — لا تنفيذ دفع فعلي</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="22" customHeight="1">
-      <c r="A79" s="11" t="inlineStr">
-        <is>
-          <t>الحساب والأمان — مجموعة جديدة</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="24" customHeight="1">
-      <c r="A80" s="12" t="inlineStr">
-        <is>
-          <t>الحساب والأمان — مجموعة جديدة</t>
-        </is>
-      </c>
-      <c r="B80" s="13" t="inlineStr">
-        <is>
-          <t>تسجيل دخول وتسجيل حساب جديد</t>
-        </is>
-      </c>
-      <c r="C80" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D80" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E80" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F80" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G80" s="18" t="inlineStr">
-        <is>
-          <t>✅ منفّذ</t>
-        </is>
-      </c>
-      <c r="H80" s="16" t="inlineStr"/>
-    </row>
-    <row r="81" ht="24" customHeight="1">
-      <c r="A81" s="12" t="inlineStr">
-        <is>
-          <t>الحساب والأمان — مجموعة جديدة</t>
-        </is>
-      </c>
-      <c r="B81" s="13" t="inlineStr">
-        <is>
-          <t>إعادة تعيين كلمة المرور بتوكن قصير الأجل</t>
-        </is>
-      </c>
-      <c r="C81" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D81" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E81" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F81" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G81" s="18" t="inlineStr">
-        <is>
-          <t>✅ منفّذ</t>
-        </is>
-      </c>
-      <c r="H81" s="16" t="inlineStr">
-        <is>
-          <t>يُبطِل باقي الجلسات</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="24" customHeight="1">
-      <c r="A82" s="12" t="inlineStr">
-        <is>
-          <t>الحساب والأمان — مجموعة جديدة</t>
-        </is>
-      </c>
-      <c r="B82" s="13" t="inlineStr">
-        <is>
-          <t>الوضع الليلي وواجهة عربية/إنجليزية</t>
-        </is>
-      </c>
-      <c r="C82" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D82" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E82" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F82" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G82" s="18" t="inlineStr">
-        <is>
-          <t>✅ منفّذ</t>
-        </is>
-      </c>
-      <c r="H82" s="16" t="inlineStr"/>
-    </row>
-    <row r="83" ht="24" customHeight="1">
-      <c r="A83" s="12" t="inlineStr">
-        <is>
-          <t>الحساب والأمان — مجموعة جديدة</t>
-        </is>
-      </c>
-      <c r="B83" s="13" t="inlineStr">
-        <is>
-          <t>التحقق بخطوتين (2FA)</t>
-        </is>
-      </c>
-      <c r="C83" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D83" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E83" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F83" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G83" s="15" t="inlineStr">
-        <is>
-          <t>⚠️ جزئي</t>
-        </is>
-      </c>
-      <c r="H83" s="16" t="inlineStr">
-        <is>
-          <t>يعمل في المتصفح بسرّ مشترك — غير آمن للإنتاج</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="24" customHeight="1">
-      <c r="A84" s="12" t="inlineStr">
-        <is>
-          <t>الحساب والأمان — مجموعة جديدة</t>
-        </is>
-      </c>
-      <c r="B84" s="13" t="inlineStr">
-        <is>
-          <t>رمز تحقق OTP بعد التسجيل</t>
-        </is>
-      </c>
-      <c r="C84" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D84" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E84" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F84" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G84" s="15" t="inlineStr">
-        <is>
-          <t>⚠️ جزئي</t>
-        </is>
-      </c>
-      <c r="H84" s="16" t="inlineStr">
-        <is>
-          <t>الرمز يظهر في لافتة على الشاشة — وضع عرض</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="24" customHeight="1">
-      <c r="A85" s="12" t="inlineStr">
-        <is>
-          <t>الحساب والأمان — مجموعة جديدة</t>
-        </is>
-      </c>
-      <c r="B85" s="13" t="inlineStr">
-        <is>
-          <t>دخول بحساب Google / Apple</t>
-        </is>
-      </c>
-      <c r="C85" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D85" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E85" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F85" s="17" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G85" s="15" t="inlineStr">
-        <is>
-          <t>⚠️ جزئي</t>
-        </is>
-      </c>
-      <c r="H85" s="16" t="inlineStr">
-        <is>
-          <t>شاشة محاكاة — لا OAuth حقيقي</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="30" customHeight="1">
-      <c r="A86" s="3" t="inlineStr">
+          <t>الحد يُضبط على القسم — لا تنبيه يُطلَق</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="3" t="inlineStr">
         <is>
           <t>الإجمالي</t>
         </is>
       </c>
-      <c r="B86" s="3" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>عدد المزايا المشمولة (✔)</t>
         </is>
       </c>
-      <c r="C86" s="3">
-        <f>COUNTIF(C5:C85,"✔")</f>
+      <c r="C74" s="3">
+        <f>COUNTIF(C5:C73,"✔")</f>
         <v/>
       </c>
-      <c r="D86" s="3">
-        <f>COUNTIF(D5:D85,"✔")</f>
+      <c r="D74" s="3">
+        <f>COUNTIF(D5:D73,"✔")</f>
         <v/>
       </c>
-      <c r="E86" s="3">
-        <f>COUNTIF(E5:E85,"✔")</f>
+      <c r="E74" s="3">
+        <f>COUNTIF(E5:E73,"✔")</f>
         <v/>
       </c>
-      <c r="F86" s="3">
-        <f>COUNTIF(F5:F85,"✔")</f>
+      <c r="F74" s="3">
+        <f>COUNTIF(F5:F73,"✔")</f>
         <v/>
       </c>
-      <c r="G86" s="3" t="inlineStr">
+      <c r="G74" s="3" t="inlineStr">
         <is>
           <t>منفّذ</t>
         </is>
       </c>
-      <c r="H86" s="3">
-        <f>COUNTIF(G5:G85,"✅ منفّذ")&amp;" منفّذ · "&amp;COUNTIF(G5:G85,"⚠️ جزئي")&amp;" جزئي · "&amp;COUNTIF(G5:G85,"❌ غير منفّذ")&amp;" غير منفّذ"</f>
+      <c r="H74" s="3">
+        <f>COUNTIF(G5:G73,"✅ منفّذ")&amp;" منفّذ · "&amp;COUNTIF(G5:G73,"⚠️ جزئي")&amp;" جزئي · "&amp;COUNTIF(G5:G73,"❌ غير منفّذ")&amp;" غير منفّذ"</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="9">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A29:H29"/>
-    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A30:H30"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A72:H72"/>
-    <mergeCell ref="A52:H52"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="A54:H54"/>
+    <mergeCell ref="A63:H63"/>
+    <mergeCell ref="A11:H11"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A79:H79"/>
-    <mergeCell ref="A61:H61"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4162,7 +3734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4404,12 +3976,12 @@
       </c>
       <c r="D12" s="23" t="inlineStr">
         <is>
-          <t>الرسائل الصوتية، تعديل الرسالة خلال 30 دقيقة، فهرسة دورات المحادثة، الأقسام بهدف SLA، الفوترة والاشتراك بالكامل، الحساب والأمان.</t>
+          <t>الرسائل الصوتية، تعديل الرسالة خلال 30 دقيقة، فهرسة دورات المحادثة، الأقسام بهدف SLA، طلب حدود مخصّصة مع تتبّع حالته، التحقق بخطوتين، تحليل الصور والمشاعر والاقتراحات الذكية.</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>أُضيفت — مجموعتان جديدتان و6 صفوف داخل المجموعات القائمة.</t>
+          <t>أُضيفت داخل المجموعات القائمة. المعيار: صفّ يستحق مكانه إذا كان يختلف بين الباقات أو يصف قدرة يشتريها العميل — لا سباكة حساب موحّدة على الكل.</t>
         </is>
       </c>
     </row>
@@ -4509,7 +4081,32 @@
       </c>
       <c r="E16" s="24" t="inlineStr">
         <is>
-          <t>لا يُطرح للعملاء قبل وصول الباكند.</t>
+          <t>لا يُطرح للعملاء قبل وصول الباكند. (2FA وحده مذكور في المصفوفة لأنه يختلف بين الباقات — الباقي لا يختلف فلا مكان له فيها.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="62" customHeight="1">
+      <c r="A17" s="25" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>بوابة الدفع غير منفّذة</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>غير مذكور</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>إعدادات Paymob ومفاتيحها موجودة في لوحة الأدمن، لكن لا يوجد تنفيذ دفع فعلي — زر «الانتقال للدفع» في تتبّع الطلب يصل لشاشة الدفع ولا يُحصّل شيئاً.</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>يحتاج باكند. البند لا يظهر في المصفوفة لأنه واحد في كل الباقات.</t>
         </is>
       </c>
     </row>

--- a/docs/Qhub - مصفوفة الباقات والمزايا.xlsx
+++ b/docs/Qhub - مصفوفة الباقات والمزايا.xlsx
@@ -11,6 +11,7 @@
     <sheet name="مصفوفة المزايا" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="توحيد المصادر" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="النواقص" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="مقارنة المنافسين" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -89,6 +90,12 @@
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00991B1B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <color rgb="00CBD5E1"/>
       <sz val="11"/>
     </font>
@@ -102,12 +109,6 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00166534"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00991B1B"/>
       <sz val="9"/>
     </font>
     <font>
@@ -155,12 +156,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCFCE7"/>
+        <fgColor rgb="00FEE2E2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEE2E2"/>
+        <fgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
     <fill>
@@ -195,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -245,17 +246,17 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -280,6 +281,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -939,82 +949,82 @@
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>القنوات المتصلة</t>
+          <t>المحادثات شهرياً</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>limits.channels</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>قناتان</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>5 قنوات</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>كل القنوات</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>كل القنوات</t>
+          <t>limits.conversations</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>بلا حد</t>
         </is>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>عدد الموظفين</t>
+          <t>القنوات المتصلة</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>limits.agents</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>20</v>
+          <t>limits.channels</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>قناتان</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>5 قنوات</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>كل القنوات</t>
+        </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>بلا حد</t>
+          <t>كل القنوات</t>
         </is>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>المحادثات شهرياً</t>
+          <t>عدد الحسابات المربوطة</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>limits.conversations</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="n">
-        <v>500</v>
-      </c>
-      <c r="D17" s="9" t="n">
-        <v>2500</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>10000</v>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
+          <t>limits.accounts — حقل ناقص في النظام</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>بلا حد</t>
         </is>
@@ -1023,26 +1033,24 @@
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>جهات الاتصال</t>
+          <t>عدد الموظفين</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>limits.contacts</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D18" s="9" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>بلا حد</t>
-        </is>
-      </c>
-      <c r="F18" s="9" t="inlineStr">
+          <t>limits.agents</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>بلا حد</t>
         </is>
@@ -1051,26 +1059,26 @@
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>الأقسام</t>
+          <t>جهات الاتصال</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>حدّ جديد — غير موجود في النظام</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
+          <t>limits.contacts</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>بلا حد</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
         <is>
           <t>بلا حد</t>
         </is>
@@ -1102,7 +1110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1192,32 +1200,32 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>القنوات المتصلة</t>
+          <t>المحادثات شهرياً</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>كم قناة تقدر تربطها بحسابك</t>
+          <t>سقف المحادثات التي يتعامل معها حسابك في الشهر — وعليه يقوم سعر الباقة</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>قناتان</t>
+          <t>500</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>5 قنوات</t>
+          <t>2,500</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>كل القنوات</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
-          <t>كل القنوات</t>
+          <t>بلا حد</t>
         </is>
       </c>
       <c r="H6" s="15" t="inlineStr">
@@ -1239,32 +1247,32 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>عدد الموظفين</t>
+          <t>القنوات المتصلة</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>كم زميل يشتغل معك على نفس الحساب</t>
+          <t>نوع القناة: واتساب، إنستغرام، بريد… كم نوعاً تفتح لك الباقة</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>قناتان</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5 قنوات</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>كل القنوات</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>بلا حد</t>
+          <t>كل القنوات</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
@@ -1286,27 +1294,27 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>المحادثات شهرياً</t>
+          <t>عدد الحسابات المربوطة</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>سقف المحادثات التي يتعامل معها حسابك في الشهر</t>
+          <t>كم حساباً فعلياً تربط — رقمَي واتساب مثلاً حسابان لا قناة واحدة</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>2,500</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -1319,9 +1327,9 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>⚠️ جزئي</t>
+      <c r="I8" s="17" t="inlineStr">
+        <is>
+          <t>❌ غير منفّذ</t>
         </is>
       </c>
     </row>
@@ -1333,27 +1341,27 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>جهات الاتصال</t>
+          <t>عدد الموظفين</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>كم عميل تقدر تحفظ بياناته</t>
+          <t>كم زميل يشتغل معك على نفس الحساب</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>بلا حد</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -1380,27 +1388,27 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>الأقسام</t>
+          <t>جهات الاتصال</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>تقسيم الفريق لمجموعات وتوجيه المحادثات لكل قسم</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>كم عميل تقدر تحفظ بياناته</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>1,000</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>بلا حد</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -1435,32 +1443,32 @@
           <t>تطلب حدوداً تناسب حجمك وتتابع حالة طلبك حتى الاشتراك</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H11" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I11" s="20" t="inlineStr">
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I11" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -1489,32 +1497,32 @@
           <t>الرد على عملائك من رقم الواتساب الرسمي</t>
         </is>
       </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H13" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I13" s="20" t="inlineStr">
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F13" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G13" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -1536,22 +1544,22 @@
           <t>نافذة محادثة تحطها في موقعك ليكلمك الزائر مباشرة</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G14" s="18" t="inlineStr">
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F14" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G14" s="19" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
@@ -1561,7 +1569,7 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="I14" s="20" t="inlineStr">
+      <c r="I14" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -1583,32 +1591,32 @@
           <t>رسائل إنستغرام تصلك في نفس الصندوق</t>
         </is>
       </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F15" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G15" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H15" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I15" s="20" t="inlineStr">
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F15" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G15" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I15" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -1630,32 +1638,32 @@
           <t>رسائل صفحتك على فيسبوك</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H16" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I16" s="20" t="inlineStr">
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F16" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G16" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -1677,32 +1685,32 @@
           <t>محادثات تيليجرام</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G17" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H17" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I17" s="20" t="inlineStr">
+      <c r="D17" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F17" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G17" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -1724,32 +1732,32 @@
           <t>Gmail و Outlook و Yahoo وأي بريد عبر SMTP</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G18" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H18" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I18" s="20" t="inlineStr">
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F18" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G18" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I18" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -1771,32 +1779,32 @@
           <t>الرسائل الخاصة على X</t>
         </is>
       </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G19" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H19" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I19" s="20" t="inlineStr">
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E19" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F19" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G19" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -1818,22 +1826,22 @@
           <t>يظهر لك طلب العميل وحالته وأنت ترد عليه</t>
         </is>
       </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G20" s="18" t="inlineStr">
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E20" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F20" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G20" s="19" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
@@ -1843,7 +1851,7 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="I20" s="20" t="inlineStr">
+      <c r="I20" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -1865,22 +1873,22 @@
           <t>نفس الربط لمتاجر شوبيفاي وووكومرس</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G21" s="18" t="inlineStr">
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E21" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G21" s="19" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
@@ -1890,7 +1898,7 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="I21" s="20" t="inlineStr">
+      <c r="I21" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -1919,32 +1927,32 @@
           <t>كل الرسائل من كل القنوات في مكان واحد، فلا تضيع محادثة</t>
         </is>
       </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F23" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G23" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H23" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I23" s="20" t="inlineStr">
+      <c r="D23" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E23" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F23" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G23" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I23" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -1966,32 +1974,32 @@
           <t>تكتب ملاحظة لزميلك داخل المحادثة لا يراها العميل</t>
         </is>
       </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G24" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H24" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I24" s="20" t="inlineStr">
+      <c r="D24" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E24" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F24" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G24" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I24" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -2013,32 +2021,32 @@
           <t>تحفظ ردودك المتكررة وترسلها بضغطة</t>
         </is>
       </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F25" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G25" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H25" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I25" s="20" t="inlineStr">
+      <c r="D25" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F25" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G25" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I25" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -2060,32 +2068,32 @@
           <t>تصنّف المحادثات بوسوم تبحث بها لاحقاً</t>
         </is>
       </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F26" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G26" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H26" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I26" s="20" t="inlineStr">
+      <c r="D26" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E26" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F26" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G26" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I26" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -2107,32 +2115,32 @@
           <t>تسجّل وترسل رسالة صوتية من داخل المحادثة</t>
         </is>
       </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F27" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G27" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H27" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I27" s="20" t="inlineStr">
+      <c r="D27" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E27" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F27" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G27" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I27" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -2154,32 +2162,32 @@
           <t>تصحّح رسالتك خلال 30 دقيقة من إرسالها</t>
         </is>
       </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F28" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G28" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H28" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I28" s="20" t="inlineStr">
+      <c r="D28" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E28" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F28" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G28" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I28" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -2208,22 +2216,22 @@
           <t>يرد على عملائك حتى خارج الدوام</t>
         </is>
       </c>
-      <c r="D30" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F30" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G30" s="18" t="inlineStr">
+      <c r="D30" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E30" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F30" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G30" s="19" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
@@ -2255,22 +2263,22 @@
           <t>يفهم العربية بلهجاتها ويرد بنفس اللهجة</t>
         </is>
       </c>
-      <c r="D31" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E31" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F31" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G31" s="18" t="inlineStr">
+      <c r="D31" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E31" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F31" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G31" s="19" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
@@ -2280,7 +2288,7 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="I31" s="20" t="inlineStr">
+      <c r="I31" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -2302,22 +2310,22 @@
           <t>ترفع منتجاتك وأسعارك وسياساتك فيرد منها لا بالتخمين</t>
         </is>
       </c>
-      <c r="D32" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E32" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F32" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G32" s="18" t="inlineStr">
+      <c r="D32" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E32" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F32" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G32" s="19" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
@@ -2327,7 +2335,7 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="I32" s="20" t="inlineStr">
+      <c r="I32" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -2349,22 +2357,22 @@
           <t>تحدّد أسلوبه: رسمي أو ودود أو مختصر، باسم علامتك</t>
         </is>
       </c>
-      <c r="D33" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E33" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F33" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G33" s="18" t="inlineStr">
+      <c r="D33" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E33" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F33" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G33" s="19" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
@@ -2374,7 +2382,7 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="I33" s="20" t="inlineStr">
+      <c r="I33" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -2396,22 +2404,22 @@
           <t>يحوّل المحادثة للموظف المناسب ومعها ملخّص جاهز</t>
         </is>
       </c>
-      <c r="D34" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E34" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F34" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G34" s="18" t="inlineStr">
+      <c r="D34" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E34" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F34" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G34" s="19" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
@@ -2421,7 +2429,7 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="I34" s="20" t="inlineStr">
+      <c r="I34" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -2443,32 +2451,32 @@
           <t>تحدّد مواضيع حسّاسة يمتنع عنها ويحوّلها للفريق</t>
         </is>
       </c>
-      <c r="D35" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E35" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F35" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G35" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H35" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I35" s="20" t="inlineStr">
+      <c r="D35" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E35" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F35" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G35" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H35" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I35" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -2490,32 +2498,32 @@
           <t>كلمات مثل «موظف» أو «شكوى» تنقل المحادثة للفريق فوراً</t>
         </is>
       </c>
-      <c r="D36" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E36" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F36" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G36" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H36" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I36" s="20" t="inlineStr">
+      <c r="D36" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E36" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F36" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G36" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H36" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I36" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -2537,7 +2545,7 @@
           <t>عدد ردود المساعد المشمولة في باقتك</t>
         </is>
       </c>
-      <c r="D37" s="17" t="inlineStr">
+      <c r="D37" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2557,7 +2565,7 @@
           <t>مخصّص</t>
         </is>
       </c>
-      <c r="H37" s="19" t="inlineStr">
+      <c r="H37" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2584,32 +2592,32 @@
           <t>نبرة وقواعد مختلفة لكل قناة على حدة</t>
         </is>
       </c>
-      <c r="D38" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E38" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F38" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G38" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H38" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I38" s="20" t="inlineStr">
+      <c r="D38" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E38" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F38" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G38" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H38" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I38" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -2631,22 +2639,22 @@
           <t>يحوّل الرسالة الصوتية إلى نص تقرأه وتبحث فيه</t>
         </is>
       </c>
-      <c r="D39" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E39" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F39" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G39" s="18" t="inlineStr">
+      <c r="D39" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E39" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F39" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G39" s="19" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
@@ -2678,27 +2686,27 @@
           <t>يفهم الصورة أو ملف PDF الذي يرسله العميل</t>
         </is>
       </c>
-      <c r="D40" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E40" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F40" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G40" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H40" s="19" t="inlineStr">
+      <c r="D40" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E40" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G40" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H40" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2725,27 +2733,27 @@
           <t>ينبّهك لما تكون نبرة العميل سلبية</t>
         </is>
       </c>
-      <c r="D41" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E41" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F41" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G41" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H41" s="19" t="inlineStr">
+      <c r="D41" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E41" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G41" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H41" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2772,27 +2780,27 @@
           <t>يقترح رداً جاهزاً للموظف قبل أن يكتب</t>
         </is>
       </c>
-      <c r="D42" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E42" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F42" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G42" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H42" s="19" t="inlineStr">
+      <c r="D42" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E42" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F42" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G42" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H42" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2819,27 +2827,27 @@
           <t>يتحسّن مع الوقت من أسلوب ردود موظفيك</t>
         </is>
       </c>
-      <c r="D43" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E43" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F43" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G43" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H43" s="19" t="inlineStr">
+      <c r="D43" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E43" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F43" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G43" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H43" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2873,22 +2881,22 @@
           <t>ترسل عرضاً أو إعلاناً لقائمة عملائك على واتساب</t>
         </is>
       </c>
-      <c r="D45" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E45" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F45" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G45" s="18" t="inlineStr">
+      <c r="D45" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E45" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F45" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G45" s="19" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
@@ -2898,7 +2906,7 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="I45" s="20" t="inlineStr">
+      <c r="I45" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -2920,22 +2928,22 @@
           <t>نفس الشيء عبر البريد</t>
         </is>
       </c>
-      <c r="D46" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E46" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F46" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G46" s="18" t="inlineStr">
+      <c r="D46" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E46" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F46" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G46" s="19" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
@@ -2945,7 +2953,7 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="I46" s="20" t="inlineStr">
+      <c r="I46" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -2967,22 +2975,22 @@
           <t>قوالب رسائل تعدّلها بدل الكتابة من الصفر</t>
         </is>
       </c>
-      <c r="D47" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E47" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F47" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G47" s="18" t="inlineStr">
+      <c r="D47" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E47" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F47" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G47" s="19" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
@@ -2992,7 +3000,7 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="I47" s="20" t="inlineStr">
+      <c r="I47" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -3014,32 +3022,32 @@
           <t>ترسل الحملة لفئة محدّدة من عملائك لا للكل</t>
         </is>
       </c>
-      <c r="D48" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E48" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F48" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G48" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H48" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I48" s="20" t="inlineStr">
+      <c r="D48" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E48" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F48" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G48" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H48" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I48" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -3061,22 +3069,22 @@
           <t>كم وصلت وكم فُتحت وكم ردّوا</t>
         </is>
       </c>
-      <c r="D49" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E49" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F49" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G49" s="18" t="inlineStr">
+      <c r="D49" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E49" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F49" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G49" s="19" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
@@ -3086,7 +3094,7 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="I49" s="20" t="inlineStr">
+      <c r="I49" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -3108,22 +3116,22 @@
           <t>تحدّد وقت الإرسال مسبقاً</t>
         </is>
       </c>
-      <c r="D50" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E50" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F50" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G50" s="18" t="inlineStr">
+      <c r="D50" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E50" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F50" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G50" s="19" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
@@ -3133,7 +3141,7 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="I50" s="20" t="inlineStr">
+      <c r="I50" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -3155,7 +3163,7 @@
           <t>سقف رسائل الحملات المشمولة — رسوم Meta منفصلة</t>
         </is>
       </c>
-      <c r="D51" s="17" t="inlineStr">
+      <c r="D51" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3175,12 +3183,12 @@
           <t>مخصّص</t>
         </is>
       </c>
-      <c r="H51" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I51" s="21" t="inlineStr">
+      <c r="H51" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I51" s="17" t="inlineStr">
         <is>
           <t>❌ غير منفّذ</t>
         </is>
@@ -3202,32 +3210,32 @@
           <t>يرسل على دفعات لحماية رقمك من الحظر</t>
         </is>
       </c>
-      <c r="D52" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E52" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F52" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G52" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H52" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I52" s="21" t="inlineStr">
+      <c r="D52" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E52" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F52" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G52" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H52" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I52" s="17" t="inlineStr">
         <is>
           <t>❌ غير منفّذ</t>
         </is>
@@ -3256,22 +3264,22 @@
           <t>تحدّد ما يشوفه وما يعمله كل موظف</t>
         </is>
       </c>
-      <c r="D54" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E54" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F54" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G54" s="18" t="inlineStr">
+      <c r="D54" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E54" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F54" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G54" s="19" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
@@ -3281,7 +3289,7 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="I54" s="20" t="inlineStr">
+      <c r="I54" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -3303,22 +3311,22 @@
           <t>رسالة تلقائية خارج أوقات عملكم</t>
         </is>
       </c>
-      <c r="D55" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E55" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F55" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G55" s="18" t="inlineStr">
+      <c r="D55" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E55" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F55" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G55" s="19" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
@@ -3328,7 +3336,7 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="I55" s="20" t="inlineStr">
+      <c r="I55" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -3350,32 +3358,32 @@
           <t>الموظف يعلن حالته فلا تصله محادثات وهو مشغول</t>
         </is>
       </c>
-      <c r="D56" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E56" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F56" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G56" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H56" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I56" s="20" t="inlineStr">
+      <c r="D56" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E56" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F56" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G56" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H56" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I56" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -3397,27 +3405,27 @@
           <t>تحدّد خلال كم دقيقة يجب أن يصل أول رد</t>
         </is>
       </c>
-      <c r="D57" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E57" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F57" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G57" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H57" s="19" t="inlineStr">
+      <c r="D57" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E57" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F57" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G57" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H57" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3444,27 +3452,27 @@
           <t>محادثة فيها كلمة «فاتورة» تروح لقسم المحاسبة</t>
         </is>
       </c>
-      <c r="D58" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E58" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F58" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G58" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H58" s="19" t="inlineStr">
+      <c r="D58" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E58" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F58" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G58" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H58" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3491,27 +3499,27 @@
           <t>تشوف من فتح ومن ردّ ومن أغلق</t>
         </is>
       </c>
-      <c r="D59" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E59" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F59" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G59" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H59" s="19" t="inlineStr">
+      <c r="D59" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E59" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F59" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G59" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H59" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3538,32 +3546,32 @@
           <t>المحادثات تتوزّع على الفريق بالتساوي</t>
         </is>
       </c>
-      <c r="D60" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E60" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F60" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G60" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H60" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I60" s="21" t="inlineStr">
+      <c r="D60" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E60" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F60" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G60" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H60" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I60" s="17" t="inlineStr">
         <is>
           <t>❌ غير منفّذ</t>
         </is>
@@ -3585,27 +3593,27 @@
           <t>طبقة حماية ثانية على حسابات فريقك</t>
         </is>
       </c>
-      <c r="D61" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E61" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F61" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G61" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H61" s="19" t="inlineStr">
+      <c r="D61" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E61" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F61" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G61" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H61" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3619,14 +3627,14 @@
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t>العملاء والتقارير</t>
+          <t>العملاء</t>
         </is>
       </c>
     </row>
     <row r="63" ht="26" customHeight="1">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>العملاء والتقارير</t>
+          <t>العملاء</t>
         </is>
       </c>
       <c r="B63" s="12" t="inlineStr">
@@ -3639,32 +3647,32 @@
           <t>كل بيانات العميل وسجل محادثاته في مكان واحد</t>
         </is>
       </c>
-      <c r="D63" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E63" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F63" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G63" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H63" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I63" s="20" t="inlineStr">
+      <c r="D63" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E63" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F63" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G63" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H63" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I63" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -3673,45 +3681,45 @@
     <row r="64" ht="26" customHeight="1">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>العملاء والتقارير</t>
+          <t>العملاء</t>
         </is>
       </c>
       <c r="B64" s="12" t="inlineStr">
         <is>
-          <t>قاعدة المعرفة</t>
+          <t>تصنيف العملاء</t>
         </is>
       </c>
       <c r="C64" s="13" t="inlineStr">
         <is>
-          <t>مقالات وأسئلة شائعة يستخدمها فريقك والمساعد</t>
-        </is>
-      </c>
-      <c r="D64" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E64" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F64" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G64" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H64" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I64" s="20" t="inlineStr">
+          <t>تقسم عملاءك لفئات تتعامل مع كل فئة بطريقة</t>
+        </is>
+      </c>
+      <c r="D64" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E64" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F64" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G64" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H64" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I64" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -3720,45 +3728,45 @@
     <row r="65" ht="26" customHeight="1">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>العملاء والتقارير</t>
+          <t>العملاء</t>
         </is>
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>تصنيف العملاء</t>
+          <t>قاعدة المعرفة</t>
         </is>
       </c>
       <c r="C65" s="13" t="inlineStr">
         <is>
-          <t>تقسم عملاءك لفئات تتعامل مع كل فئة بطريقة</t>
-        </is>
-      </c>
-      <c r="D65" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E65" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F65" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G65" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H65" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I65" s="20" t="inlineStr">
+          <t>مقالات وأسئلة شائعة يستخدمها فريقك والمساعد</t>
+        </is>
+      </c>
+      <c r="D65" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E65" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F65" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G65" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H65" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I65" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -3767,37 +3775,37 @@
     <row r="66" ht="26" customHeight="1">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>العملاء والتقارير</t>
+          <t>العملاء</t>
         </is>
       </c>
       <c r="B66" s="12" t="inlineStr">
         <is>
-          <t>تقارير الأداء</t>
+          <t>تقييمات العملاء</t>
         </is>
       </c>
       <c r="C66" s="13" t="inlineStr">
         <is>
-          <t>لوحة تشوف فيها حجم العمل وأداء الفريق</t>
-        </is>
-      </c>
-      <c r="D66" s="14" t="inlineStr">
-        <is>
-          <t>أساسية</t>
-        </is>
-      </c>
-      <c r="E66" s="14" t="inlineStr">
-        <is>
-          <t>متقدّمة</t>
-        </is>
-      </c>
-      <c r="F66" s="14" t="inlineStr">
-        <is>
-          <t>متقدّمة</t>
-        </is>
-      </c>
-      <c r="G66" s="14" t="inlineStr">
-        <is>
-          <t>متقدّمة</t>
+          <t>يقيّم العميل الخدمة بعد إغلاق المحادثة</t>
+        </is>
+      </c>
+      <c r="D66" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E66" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F66" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G66" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
         </is>
       </c>
       <c r="H66" s="15" t="inlineStr">
@@ -3805,7 +3813,7 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="I66" s="20" t="inlineStr">
+      <c r="I66" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -3814,45 +3822,45 @@
     <row r="67" ht="26" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>العملاء والتقارير</t>
+          <t>العملاء</t>
         </is>
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>متوسط زمن أول رد</t>
+          <t>الشكاوى والاقتراحات</t>
         </is>
       </c>
       <c r="C67" s="13" t="inlineStr">
         <is>
-          <t>كم يستنى عميلك قبل أول رد</t>
+          <t>صندوق منفصل للشكاوى تتابعه حتى الإغلاق</t>
         </is>
       </c>
       <c r="D67" s="18" t="inlineStr">
         <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E67" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F67" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G67" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H67" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I67" s="20" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E67" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F67" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G67" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H67" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I67" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -3861,139 +3869,99 @@
     <row r="68" ht="26" customHeight="1">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>العملاء والتقارير</t>
+          <t>العملاء</t>
         </is>
       </c>
       <c r="B68" s="12" t="inlineStr">
         <is>
-          <t>ساعات الذروة</t>
+          <t>سجل نشاط العميل</t>
         </is>
       </c>
       <c r="C68" s="13" t="inlineStr">
         <is>
-          <t>أي ساعات اليوم أكثر ضغطاً لتوزّع فريقك عليها</t>
-        </is>
-      </c>
-      <c r="D68" s="17" t="inlineStr">
+          <t>كل ما عمله العميل معك بالترتيب الزمني</t>
+        </is>
+      </c>
+      <c r="D68" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="E68" s="18" t="inlineStr">
         <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F68" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G68" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H68" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I68" s="20" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F68" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G68" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H68" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I68" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="26" customHeight="1">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>العملاء والتقارير</t>
-        </is>
-      </c>
-      <c r="B69" s="12" t="inlineStr">
-        <is>
-          <t>تقييمات العملاء</t>
-        </is>
-      </c>
-      <c r="C69" s="13" t="inlineStr">
-        <is>
-          <t>يقيّم العميل الخدمة بعد إغلاق المحادثة</t>
-        </is>
-      </c>
-      <c r="D69" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E69" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F69" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G69" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H69" s="15" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="I69" s="20" t="inlineStr">
-        <is>
-          <t>✅ منفّذ</t>
+    <row r="69" ht="22" customHeight="1">
+      <c r="A69" s="11" t="inlineStr">
+        <is>
+          <t>التقارير</t>
         </is>
       </c>
     </row>
     <row r="70" ht="26" customHeight="1">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>العملاء والتقارير</t>
+          <t>التقارير</t>
         </is>
       </c>
       <c r="B70" s="12" t="inlineStr">
         <is>
-          <t>الشكاوى والاقتراحات</t>
+          <t>تقارير الأداء</t>
         </is>
       </c>
       <c r="C70" s="13" t="inlineStr">
         <is>
-          <t>صندوق منفصل للشكاوى تتابعه حتى الإغلاق</t>
-        </is>
-      </c>
-      <c r="D70" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F70" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G70" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H70" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I70" s="20" t="inlineStr">
+          <t>لوحة تشوف فيها حجم العمل وأداء الفريق</t>
+        </is>
+      </c>
+      <c r="D70" s="14" t="inlineStr">
+        <is>
+          <t>أساسية</t>
+        </is>
+      </c>
+      <c r="E70" s="14" t="inlineStr">
+        <is>
+          <t>متقدّمة</t>
+        </is>
+      </c>
+      <c r="F70" s="14" t="inlineStr">
+        <is>
+          <t>متقدّمة</t>
+        </is>
+      </c>
+      <c r="G70" s="14" t="inlineStr">
+        <is>
+          <t>متقدّمة</t>
+        </is>
+      </c>
+      <c r="H70" s="15" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="I70" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -4002,45 +3970,45 @@
     <row r="71" ht="26" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>العملاء والتقارير</t>
+          <t>التقارير</t>
         </is>
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>سجل نشاط العميل</t>
+          <t>متوسط زمن أول رد</t>
         </is>
       </c>
       <c r="C71" s="13" t="inlineStr">
         <is>
-          <t>كل ما عمله العميل معك بالترتيب الزمني</t>
-        </is>
-      </c>
-      <c r="D71" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G71" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H71" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I71" s="20" t="inlineStr">
+          <t>كم يستنى عميلك قبل أول رد</t>
+        </is>
+      </c>
+      <c r="D71" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E71" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F71" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G71" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H71" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
@@ -4049,148 +4017,148 @@
     <row r="72" ht="26" customHeight="1">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>العملاء والتقارير</t>
+          <t>التقارير</t>
         </is>
       </c>
       <c r="B72" s="12" t="inlineStr">
         <is>
-          <t>تنبيه عند تأخّر الرد</t>
+          <t>ساعات الذروة</t>
         </is>
       </c>
       <c r="C72" s="13" t="inlineStr">
         <is>
-          <t>ينبّهك لما تتجاوز محادثة الوقت المسموح</t>
-        </is>
-      </c>
-      <c r="D72" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E72" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F72" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G72" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H72" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I72" s="16" t="inlineStr">
-        <is>
-          <t>⚠️ جزئي</t>
+          <t>أي ساعات اليوم أكثر ضغطاً لتوزّع فريقك عليها</t>
+        </is>
+      </c>
+      <c r="D72" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F72" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G72" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H72" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="21" t="inlineStr">
+        <is>
+          <t>✅ منفّذ</t>
         </is>
       </c>
     </row>
     <row r="73" ht="26" customHeight="1">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>العملاء والتقارير</t>
+          <t>التقارير</t>
         </is>
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
+          <t>تنبيه عند تأخّر الرد</t>
+        </is>
+      </c>
+      <c r="C73" s="13" t="inlineStr">
+        <is>
+          <t>ينبّهك لما تتجاوز محادثة الوقت المسموح</t>
+        </is>
+      </c>
+      <c r="D73" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G73" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H73" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="16" t="inlineStr">
+        <is>
+          <t>⚠️ جزئي</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="26" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>التقارير</t>
+        </is>
+      </c>
+      <c r="B74" s="12" t="inlineStr">
+        <is>
           <t>تصدير التقارير</t>
         </is>
       </c>
-      <c r="C73" s="13" t="inlineStr">
+      <c r="C74" s="13" t="inlineStr">
         <is>
           <t>تنزّل تقاريرك ملف CSV</t>
         </is>
       </c>
-      <c r="D73" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G73" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H73" s="15" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="I73" s="20" t="inlineStr">
+      <c r="D74" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G74" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H74" s="15" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="I74" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="22" customHeight="1">
-      <c r="A74" s="11" t="inlineStr">
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="11" t="inlineStr">
         <is>
           <t>الربط والدعم</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="26" customHeight="1">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>الربط والدعم</t>
-        </is>
-      </c>
-      <c r="B75" s="12" t="inlineStr">
-        <is>
-          <t>تكامل API</t>
-        </is>
-      </c>
-      <c r="C75" s="13" t="inlineStr">
-        <is>
-          <t>تربط Qhub بأنظمتك الأخرى</t>
-        </is>
-      </c>
-      <c r="D75" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E75" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F75" s="14" t="inlineStr">
-        <is>
-          <t>محدود</t>
-        </is>
-      </c>
-      <c r="G75" s="14" t="inlineStr">
-        <is>
-          <t>كامل</t>
-        </is>
-      </c>
-      <c r="H75" s="15" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="I75" s="16" t="inlineStr">
-        <is>
-          <t>⚠️ جزئي</t>
         </is>
       </c>
     </row>
@@ -4202,32 +4170,32 @@
       </c>
       <c r="B76" s="12" t="inlineStr">
         <is>
-          <t>الدعم</t>
+          <t>تكامل API</t>
         </is>
       </c>
       <c r="C76" s="13" t="inlineStr">
         <is>
-          <t>كيف تتواصل معنا لما تحتاج مساعدة</t>
-        </is>
-      </c>
-      <c r="D76" s="14" t="inlineStr">
-        <is>
-          <t>بريد إلكتروني</t>
-        </is>
-      </c>
-      <c r="E76" s="14" t="inlineStr">
-        <is>
-          <t>أولوية</t>
+          <t>تربط Qhub بأنظمتك الأخرى</t>
+        </is>
+      </c>
+      <c r="D76" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E76" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>أولوية</t>
+          <t>محدود</t>
         </is>
       </c>
       <c r="G76" s="14" t="inlineStr">
         <is>
-          <t>مدير حساب</t>
+          <t>كامل</t>
         </is>
       </c>
       <c r="H76" s="15" t="inlineStr">
@@ -4249,95 +4217,143 @@
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
+          <t>الدعم</t>
+        </is>
+      </c>
+      <c r="C77" s="13" t="inlineStr">
+        <is>
+          <t>كيف تتواصل معنا لما تحتاج مساعدة</t>
+        </is>
+      </c>
+      <c r="D77" s="14" t="inlineStr">
+        <is>
+          <t>بريد إلكتروني</t>
+        </is>
+      </c>
+      <c r="E77" s="14" t="inlineStr">
+        <is>
+          <t>أولوية</t>
+        </is>
+      </c>
+      <c r="F77" s="14" t="inlineStr">
+        <is>
+          <t>أولوية</t>
+        </is>
+      </c>
+      <c r="G77" s="14" t="inlineStr">
+        <is>
+          <t>مدير حساب</t>
+        </is>
+      </c>
+      <c r="H77" s="15" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="I77" s="16" t="inlineStr">
+        <is>
+          <t>⚠️ جزئي</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="26" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>الربط والدعم</t>
+        </is>
+      </c>
+      <c r="B78" s="12" t="inlineStr">
+        <is>
           <t>اتفاقية مستوى خدمة (SLA)</t>
         </is>
       </c>
-      <c r="C77" s="13" t="inlineStr">
+      <c r="C78" s="13" t="inlineStr">
         <is>
           <t>التزام تعاقدي بزمن الرد ونسبة التشغيل</t>
         </is>
       </c>
-      <c r="D77" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E77" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F77" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G77" s="18" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H77" s="15" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="I77" s="21" t="inlineStr">
+      <c r="D78" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H78" s="15" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="I78" s="17" t="inlineStr">
         <is>
           <t>❌ غير منفّذ</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="30" customHeight="1">
-      <c r="A78" s="3" t="inlineStr">
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>الإجمالي</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
+      <c r="B79" s="3" t="inlineStr">
         <is>
           <t>المشمول في كل باقة</t>
         </is>
       </c>
-      <c r="C78" s="3">
-        <f>COUNTIF(H5:H77,"✔")&amp;" صفاً تظهر على الموقع"</f>
+      <c r="C79" s="3">
+        <f>COUNTIF(H5:H78,"✔")&amp;" صفاً تظهر على الموقع"</f>
         <v/>
       </c>
-      <c r="D78" s="3">
-        <f>COUNTIF(D5:D77,"✔")</f>
+      <c r="D79" s="3">
+        <f>COUNTIF(D5:D78,"✔")</f>
         <v/>
       </c>
-      <c r="E78" s="3">
-        <f>COUNTIF(E5:E77,"✔")</f>
+      <c r="E79" s="3">
+        <f>COUNTIF(E5:E78,"✔")</f>
         <v/>
       </c>
-      <c r="F78" s="3">
-        <f>COUNTIF(F5:F77,"✔")</f>
+      <c r="F79" s="3">
+        <f>COUNTIF(F5:F78,"✔")</f>
         <v/>
       </c>
-      <c r="G78" s="3">
-        <f>COUNTIF(G5:G77,"✔")</f>
+      <c r="G79" s="3">
+        <f>COUNTIF(G5:G78,"✔")</f>
         <v/>
       </c>
-      <c r="H78" s="3">
-        <f>COUNTIF(H5:H77,"✔")</f>
+      <c r="H79" s="3">
+        <f>COUNTIF(H5:H78,"✔")</f>
         <v/>
       </c>
-      <c r="I78" s="3">
-        <f>COUNTIF(I5:I77,"✅ منفّذ")&amp;" / "&amp;COUNTIF(I5:I77,"⚠️ جزئي")&amp;" / "&amp;COUNTIF(I5:I77,"❌ غير منفّذ")</f>
+      <c r="I79" s="3">
+        <f>COUNTIF(I5:I78,"✅ منفّذ")&amp;" / "&amp;COUNTIF(I5:I78,"⚠️ جزئي")&amp;" / "&amp;COUNTIF(I5:I78,"❌ غير منفّذ")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A29:I29"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A75:I75"/>
     <mergeCell ref="A44:I44"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A53:I53"/>
     <mergeCell ref="A22:I22"/>
-    <mergeCell ref="A74:I74"/>
+    <mergeCell ref="A69:I69"/>
     <mergeCell ref="A12:I12"/>
     <mergeCell ref="A62:I62"/>
   </mergeCells>
@@ -4429,7 +4445,7 @@
           <t>المبتدئ</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr">
         <is>
           <t>البداية</t>
         </is>
@@ -4461,7 +4477,7 @@
           <t>الاحترافي</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>الاحترافية</t>
         </is>
@@ -4493,7 +4509,7 @@
           <t>19 / 49 / 99 / 249</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>19 / 49 / 99 / 249</t>
         </is>
@@ -4525,7 +4541,7 @@
           <t>1 / 3 / 10 / بلا حد</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>2 / 5 / الكل / الكل</t>
         </is>
@@ -4557,7 +4573,7 @@
           <t>3 / 10 / 25 / بلا حد</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>2 / 7 / 20 / بلا حد</t>
         </is>
@@ -4589,7 +4605,7 @@
           <t>1,000 / 10,000 / 50,000 / بلا حد</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>500 / 2,500 / 10,000 / بلا حد</t>
         </is>
@@ -4621,7 +4637,7 @@
           <t>500 / بلا حد / بلا حد / بلا حد</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>1,000 / 10,000 / بلا حد / بلا حد</t>
         </is>
@@ -4635,7 +4651,7 @@
     <row r="12" ht="40" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>الأقسام</t>
+          <t>حدّ الأقسام</t>
         </is>
       </c>
       <c r="B12" s="22" t="inlineStr">
@@ -4650,24 +4666,24 @@
       </c>
       <c r="D12" s="22" t="inlineStr">
         <is>
-          <t>الأقسام موجودة بلا حدّ للباقة</t>
-        </is>
-      </c>
-      <c r="E12" s="20" t="inlineStr">
-        <is>
-          <t>— / 3 / 10 / بلا حد</t>
+          <t>محذوف عمداً — قرار سابق</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>محذوف</t>
         </is>
       </c>
       <c r="F12" s="23" t="inlineStr">
         <is>
-          <t>إضافة limits.departments للنوع Plan — حدّ جديد بالكامل</t>
+          <t>إزالة صف «الأقسام» من جدول المقارنة في pricing.ts — الموقع لا يزال يعرض حدّاً أُلغي</t>
         </is>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>عدد الحسابات</t>
+          <t>عدد الحسابات المربوطة</t>
         </is>
       </c>
       <c r="B13" s="22" t="inlineStr">
@@ -4682,17 +4698,17 @@
       </c>
       <c r="D13" s="22" t="inlineStr">
         <is>
-          <t>لا وجود لهذا المفهوم</t>
-        </is>
-      </c>
-      <c r="E13" s="20" t="inlineStr">
-        <is>
-          <t>محذوف</t>
+          <t>لا وجود لهذا الحدّ</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>1 / 2 / 5 / بلا حد</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t>لا شيء — البند شُطب، لا معنى له إلى جانب عدد الموظفين</t>
+          <t>إضافة limits.accounts للنوع Plan، وإضافة الصف لجدول الموقع. حدّ مستقل عن القنوات: رقمَا واتساب = قناة واحدة وحسابان.</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4733,7 @@
           <t>سعر معروض 249$ واشتراك ذاتي</t>
         </is>
       </c>
-      <c r="E14" s="20" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>بالتواصل مع المبيعات</t>
         </is>
@@ -4743,7 +4759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4834,17 +4850,17 @@
       </c>
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>حدّ الأقسام غير موجود أصلاً</t>
+          <t>عدد الحسابات المربوطة بلا حقل</t>
         </is>
       </c>
       <c r="C7" s="26" t="inlineStr">
         <is>
-          <t>الأقسام مبنية وتشتغل، لكن النوع Plan ما فيه limits.departments — فما في رقم يُقاس عليه.</t>
+          <t>حدّ مطلوب ومتّفق عليه، والنوع Plan ما فيه limits.accounts. القنوات في النظام صفوف مستقلة من نوع Channel، فربط رقمَي واتساب يُنشئ سجلّين تحت نوع واحد — أي أن التمييز بين «القناة» و«الحساب» قائم في البيانات وينقصه الحدّ فقط.</t>
         </is>
       </c>
       <c r="D7" s="27" t="inlineStr">
         <is>
-          <t>إضافة الحقل للنوع وللباقات الأربع قبل عرض الصف على الموقع.</t>
+          <t>إضافة limits.accounts للنوع وللباقات الأربع. أقرب حدّ للتنفيذ لأن البيانات جاهزة — يكفي عدّ سجلات Channel.</t>
         </is>
       </c>
     </row>
@@ -4854,17 +4870,17 @@
       </c>
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>تفريغ الرسائل الصوتية غير عامل</t>
+          <t>الموقع يعرض حدّاً محذوفاً</t>
         </is>
       </c>
       <c r="C8" s="26" t="inlineStr">
         <is>
-          <t>الواجهة كاملة، لكن transcribeAudio تُرجع نصاً ثابتاً، ولا شيء في التطبيق يشغّل المسار أصلاً.</t>
+          <t>جدول المقارنة في pricing.ts فيه صف «الأقسام: — / 3 / 10 / بلا حد»، وهذا الحدّ أُلغي عندنا عمداً.</t>
         </is>
       </c>
       <c r="D8" s="27" t="inlineStr">
         <is>
-          <t>يحتاج باكند — مفتاح المزوّد لا يوضع في المتصفح. البند معروض على الموقع اليوم.</t>
+          <t>حذف الصف من الموقع — نحن نَعِد بحدّ لم يعد موجوداً.</t>
         </is>
       </c>
     </row>
@@ -4874,17 +4890,17 @@
       </c>
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>المساعد الذكي كله يعتمد على دالة وهمية</t>
+          <t>تفريغ الرسائل الصوتية غير عامل</t>
         </is>
       </c>
       <c r="C9" s="26" t="inlineStr">
         <is>
-          <t>getAIResponse في utils/ai.ts تُرجع نصاً ثابتاً. كل صفوف «ردود تلقائية» و«اقتراح الرد» و«قراءة الصور» و«قياس الرضا» مفاتيح في الإعدادات بلا منطق خلفها.</t>
+          <t>الواجهة كاملة، لكن transcribeAudio تُرجع نصاً ثابتاً، ولا شيء في التطبيق يشغّل المسار أصلاً.</t>
         </is>
       </c>
       <c r="D9" s="27" t="inlineStr">
         <is>
-          <t>يحتاج باكند. الإعدادات والواجهات جاهزة بالكامل، ينقص الربط.</t>
+          <t>يحتاج باكند — مفتاح المزوّد لا يوضع في المتصفح. البند معروض على الموقع اليوم.</t>
         </is>
       </c>
     </row>
@@ -4894,17 +4910,17 @@
       </c>
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>أربع مزايا بلا أثر في الكود</t>
+          <t>المساعد الذكي كله يعتمد على دالة وهمية</t>
         </is>
       </c>
       <c r="C10" s="26" t="inlineStr">
         <is>
-          <t>توزيع تلقائي متوازن · إرسال تدريجي · سقف رسائل الحملات · اتفاقية SLA. ولا واحدة منها لها سطر واحد.</t>
+          <t>getAIResponse في utils/ai.ts تُرجع نصاً ثابتاً. كل صفوف «ردود تلقائية» و«اقتراح الرد» و«قراءة الصور» و«قياس الرضا» مفاتيح في الإعدادات بلا منطق خلفها.</t>
         </is>
       </c>
       <c r="D10" s="27" t="inlineStr">
         <is>
-          <t>إما تُبنى أو تُشطب من العرض. اثنتان منها معروضتان على الموقع اليوم.</t>
+          <t>يحتاج باكند. الإعدادات والواجهات جاهزة بالكامل، ينقص الربط.</t>
         </is>
       </c>
     </row>
@@ -4914,17 +4930,17 @@
       </c>
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>بنود تُضبط ولا تُنفَّذ</t>
+          <t>أربع مزايا بلا أثر في الكود</t>
         </is>
       </c>
       <c r="C11" s="26" t="inlineStr">
         <is>
-          <t>هدف زمن الاستجابة يُحفظ على القسم ولا تنبيه يُطلَق · كلمات التوجيه routingKeywords تُحفظ ولا كود يقرأها · سجلّ الإجراءات على مستوى المحادثة لا الموظف.</t>
+          <t>توزيع تلقائي متوازن · إرسال تدريجي · سقف رسائل الحملات · اتفاقية SLA. ولا واحدة منها لها سطر واحد.</t>
         </is>
       </c>
       <c r="D11" s="27" t="inlineStr">
         <is>
-          <t>ثلاثة بنود قريبة الإنجاز — الحقول موجودة، ينقص المنطق.</t>
+          <t>إما تُبنى أو تُشطب من العرض. اثنتان منها معروضتان على الموقع اليوم.</t>
         </is>
       </c>
     </row>
@@ -4934,17 +4950,17 @@
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>بوابة الدفع غير منفّذة</t>
+          <t>بنود تُضبط ولا تُنفَّذ</t>
         </is>
       </c>
       <c r="C12" s="26" t="inlineStr">
         <is>
-          <t>إعدادات Paymob ومفاتيحها موجودة، لكن زر «الانتقال للدفع» يصل لشاشة الدفع ولا يُحصّل شيئاً.</t>
+          <t>هدف زمن الاستجابة يُحفظ على القسم ولا تنبيه يُطلَق · كلمات التوجيه routingKeywords تُحفظ ولا كود يقرأها · سجلّ الإجراءات على مستوى المحادثة لا الموظف.</t>
         </is>
       </c>
       <c r="D12" s="27" t="inlineStr">
         <is>
-          <t>يحتاج باكند. لا يظهر في المصفوفة لأنه واحد في كل الباقات.</t>
+          <t>ثلاثة بنود قريبة الإنجاز — الحقول موجودة، ينقص المنطق.</t>
         </is>
       </c>
     </row>
@@ -4954,17 +4970,17 @@
       </c>
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>الأمان في وضع عرض</t>
+          <t>بوابة الدفع غير منفّذة</t>
         </is>
       </c>
       <c r="C13" s="26" t="inlineStr">
         <is>
-          <t>التحقق بخطوتين يعمل في المتصفح بسرّ مشترك · رمز OTP يظهر في لافتة على الشاشة · دخول Google و Apple شاشة محاكاة بلا OAuth.</t>
+          <t>إعدادات Paymob ومفاتيحها موجودة، لكن زر «الانتقال للدفع» يصل لشاشة الدفع ولا يُحصّل شيئاً.</t>
         </is>
       </c>
       <c r="D13" s="27" t="inlineStr">
         <is>
-          <t>لا يُطرح للعملاء قبل الباكند. التحقق بخطوتين وحده مذكور في المصفوفة لأنه يختلف بين الباقات.</t>
+          <t>يحتاج باكند. لا يظهر في المصفوفة لأنه واحد في كل الباقات.</t>
         </is>
       </c>
     </row>
@@ -4974,17 +4990,17 @@
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>التجربة المجانية: 7 أيام أم 14؟</t>
+          <t>الأمان في وضع عرض</t>
         </is>
       </c>
       <c r="C14" s="26" t="inlineStr">
         <is>
-          <t>صفحة الأسعار تَعِد بـ«7 أيام مجاناً دون بطاقة». النظام يعرف الحالة التجريبية (ClientStatus «trial» و trialEndsAt)، لكن الأدمن وحده يفتحها يدوياً من شاشة العملاء — و**بمدة 14 يوماً** لا 7. التسجيل الذاتي لا ينشئ تجربة إطلاقاً، ولا شيء ينهيها عند انقضائها.</t>
+          <t>التحقق بخطوتين يعمل في المتصفح بسرّ مشترك · رمز OTP يظهر في لافتة على الشاشة · دخول Google و Apple شاشة محاكاة بلا OAuth.</t>
         </is>
       </c>
       <c r="D14" s="27" t="inlineStr">
         <is>
-          <t>ثلاثة قرارات: توحيد المدة (7 أم 14)، وبدء التجربة تلقائياً عند التسجيل، وما الذي يحدث عند انتهائها.</t>
+          <t>لا يُطرح للعملاء قبل الباكند. التحقق بخطوتين وحده مذكور في المصفوفة لأنه يختلف بين الباقات.</t>
         </is>
       </c>
     </row>
@@ -4994,15 +5010,35 @@
       </c>
       <c r="B15" s="25" t="inlineStr">
         <is>
+          <t>التجربة المجانية: 7 أيام أم 14؟</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>صفحة الأسعار تَعِد بـ«7 أيام مجاناً دون بطاقة». النظام يعرف الحالة التجريبية (ClientStatus «trial» و trialEndsAt)، لكن الأدمن وحده يفتحها يدوياً من شاشة العملاء — و**بمدة 14 يوماً** لا 7. التسجيل الذاتي لا ينشئ تجربة إطلاقاً، ولا شيء ينهيها عند انقضائها.</t>
+        </is>
+      </c>
+      <c r="D15" s="27" t="inlineStr">
+        <is>
+          <t>ثلاثة قرارات: توحيد المدة (7 أم 14)، وبدء التجربة تلقائياً عند التسجيل، وما الذي يحدث عند انتهائها.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="56" customHeight="1">
+      <c r="A16" s="28" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="25" t="inlineStr">
+        <is>
           <t>مزايا مبنية وغير معروضة</t>
         </is>
       </c>
-      <c r="C15" s="26" t="inlineStr">
+      <c r="C16" s="26" t="inlineStr">
         <is>
           <t>الرسائل الصوتية · تعديل الرسالة خلال 30 دقيقة · فهرسة دورات المحادثة · حالة متاح ومشغول · تصدير التقارير.</t>
         </is>
       </c>
-      <c r="D15" s="27" t="inlineStr">
+      <c r="D16" s="27" t="inlineStr">
         <is>
           <t>أُضيفت للمصفوفة. يستحق بعضها الظهور على الموقع — قرار تسويقي.</t>
         </is>
@@ -5015,4 +5051,483 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ما عند المنافسين وما ينقصنا</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>BEON من لقطة شاشة صفحة الباقات · respond.io من صفحة أسعارها ومراجعات 2026 (الدومين محجوب عن الوكيل، فالأرقام من مصادر ثانوية وتحتاج تأكيداً)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>البند</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>BEON</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>respond.io</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>عندنا</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>التوصية</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="54" customHeight="1">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>وحدة التسعير</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>Conversations (MAC) — جهات اتصال نشطة شهرياً</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>Monthly Active Contacts — نفس المفهوم، وهو المحور الأول للسعر</t>
+        </is>
+      </c>
+      <c r="D5" s="29" t="inlineStr">
+        <is>
+          <t>محادثات خام شهرياً</t>
+        </is>
+      </c>
+      <c r="E5" s="27" t="inlineStr">
+        <is>
+          <t>ندرس التحوّل لـ«جهة اتصال نشطة»: العميل الذي يراسلك 20 مرة يُحتسب مرة، وهو أعدل وأسهل تنبّؤاً — والمنافسان اتفقا عليه.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="54" customHeight="1">
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>المحور الثاني للسعر</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>Agents ثابت لكل باقة</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="inlineStr">
+        <is>
+          <t>Users (مقاعد) — تُشترى إضافية بـ12–24$ للمقعد شهرياً</t>
+        </is>
+      </c>
+      <c r="D6" s="29" t="inlineStr">
+        <is>
+          <t>موظفون بعدد ثابت لا يُزاد</t>
+        </is>
+      </c>
+      <c r="E6" s="27" t="inlineStr">
+        <is>
+          <t>بيع مقعد إضافي دون ترقية الباقة — مصدر دخل مباشر ويمنع ترقية قسرية تُنفّر العميل.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>تجاوز الحدّ</t>
+        </is>
+      </c>
+      <c r="B7" s="26" t="inlineStr">
+        <is>
+          <t>غير ظاهر</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="inlineStr">
+        <is>
+          <t>رسوم تجاوز: 12$ لكل 100 جهة على Growth و15$ على Advanced</t>
+        </is>
+      </c>
+      <c r="D7" s="29" t="inlineStr">
+        <is>
+          <t>لا حدّ يُطبَّق أصلاً</t>
+        </is>
+      </c>
+      <c r="E7" s="27" t="inlineStr">
+        <is>
+          <t>القرار الأهم: عند التجاوز نمنع أم نحاسب؟ respond.io تحاسب ولا توقف الخدمة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="25" t="inlineStr">
+        <is>
+          <t>صناديق الوارد / الحسابات</t>
+        </is>
+      </c>
+      <c r="B8" s="26" t="inlineStr">
+        <is>
+          <t>Inboxes حدّ صريح: 4 / 10 / 10 / 5 / 1</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t>تعدّد مساحات العمل على Advanced</t>
+        </is>
+      </c>
+      <c r="D8" s="29" t="inlineStr">
+        <is>
+          <t>الحدّ غائب — وهو «عدد الحسابات» المطلوب</t>
+        </is>
+      </c>
+      <c r="E8" s="27" t="inlineStr">
+        <is>
+          <t>يؤكّد قرارك: الحدّ ضروري وله سابقة عند المنافسين.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>البثّ / الحملات</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>Broadcasts حصّة مستقلة: 50 / 5k / 10k / 25k</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>البثّ لا يُفتح إلا من Growth فما فوق</t>
+        </is>
+      </c>
+      <c r="D9" s="29" t="inlineStr">
+        <is>
+          <t>الحملات مبنية بلا حصّة</t>
+        </is>
+      </c>
+      <c r="E9" s="27" t="inlineStr">
+        <is>
+          <t>إضافة حصّة رسائل حملات للباقة — عندنا الصف في المصفوفة بلا حقل وراءه.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="54" customHeight="1">
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>حصص الذكاء الاصطناعي</t>
+        </is>
+      </c>
+      <c r="B10" s="26" t="inlineStr">
+        <is>
+          <t>حصّتان منفصلتان: AI Tokens و AI QA</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>أرصدة AI تكبر مع شريحة جهات الاتصال</t>
+        </is>
+      </c>
+      <c r="D10" s="30" t="inlineStr">
+        <is>
+          <t>رصيد واحد في الإعدادات غير مربوط بالباقة</t>
+        </is>
+      </c>
+      <c r="E10" s="27" t="inlineStr">
+        <is>
+          <t>ربط الرصيد بالباقة، وفصل «ردود» عن «تحليل» إن اختلفت كلفتهما.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="54" customHeight="1">
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>بناء الأتمتة</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>Workflow Builds و Workflow Runs حصّتان</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>Workflows محور رئيسي — ومعها HTTP requests على Advanced</t>
+        </is>
+      </c>
+      <c r="D11" s="29" t="inlineStr">
+        <is>
+          <t>لا يوجد بانٍ أتمتة إطلاقاً</t>
+        </is>
+      </c>
+      <c r="E11" s="27" t="inlineStr">
+        <is>
+          <t>أكبر فجوة وظيفية. عندنا توجيه بكلمة مفتاحية فقط، وهما عندهما محرّك كامل.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="54" customHeight="1">
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t>وكلاء AI</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>غير ظاهر</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>AI Agents — وكيل يدير المحادثة لا مجرّد ردّ آلي</t>
+        </is>
+      </c>
+      <c r="D12" s="29" t="inlineStr">
+        <is>
+          <t>مساعد يردّ ويحوّل</t>
+        </is>
+      </c>
+      <c r="E12" s="27" t="inlineStr">
+        <is>
+          <t>الفرق تسويقي بقدر ما هو تقني — «وكيل» أقوى من «ردّ تلقائي».</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="54" customHeight="1">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>رصيد OTP و SMS</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>OTP Balance و SMS Balance حصّتان</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>SMS قناة مستقلة</t>
+        </is>
+      </c>
+      <c r="D13" s="30" t="inlineStr">
+        <is>
+          <t>لا يوجد</t>
+        </is>
+      </c>
+      <c r="E13" s="27" t="inlineStr">
+        <is>
+          <t>فرصة دخل إضافي، ومطلوبة لأي تحقّق برقم الجوال.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="54" customHeight="1">
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t>باقة مجانية دائمة</t>
+        </is>
+      </c>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>Free forever — 50 محادثة و1 موظف و4 صناديق</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>تجربة 7 أيام فقط</t>
+        </is>
+      </c>
+      <c r="D14" s="30" t="inlineStr">
+        <is>
+          <t>تجربة يفتحها الأدمن يدوياً 14 يوماً</t>
+        </is>
+      </c>
+      <c r="E14" s="27" t="inlineStr">
+        <is>
+          <t>باقة مجانية دائمة أقوى قمع استحواذ من تجربة مؤقتة — قرار تجاري.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="54" customHeight="1">
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>باقات مخصّصة بالاسم</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>باقة باسم العميل: «Adel Sedik English Academy»</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>Enterprise بترتيب مخصّص</t>
+        </is>
+      </c>
+      <c r="D15" s="30" t="inlineStr">
+        <is>
+          <t>مسار طلب حدود مخصّصة مبني بالكامل</t>
+        </is>
+      </c>
+      <c r="E15" s="27" t="inlineStr">
+        <is>
+          <t>نحن جاهزون هنا — ينقص فقط أن يُنشئ الأدمن باقة خاصة بعد الموافقة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="54" customHeight="1">
+      <c r="A16" s="25" t="inlineStr">
+        <is>
+          <t>باقات حسب المجال</t>
+        </is>
+      </c>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>نسخ E-Commerce من كل باقة بحدود مختلفة</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>غير ظاهر</t>
+        </is>
+      </c>
+      <c r="D16" s="29" t="inlineStr">
+        <is>
+          <t>باقة واحدة للجميع</t>
+        </is>
+      </c>
+      <c r="E16" s="27" t="inlineStr">
+        <is>
+          <t>يستحق الدراسة: عندنا سلة وزد وشوبيفاي — باقة تجارة إلكترونية منطقية.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="54" customHeight="1">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>تسجيل دخول موحّد SSO</t>
+        </is>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>غير ظاهر</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>SSO على Advanced</t>
+        </is>
+      </c>
+      <c r="D17" s="29" t="inlineStr">
+        <is>
+          <t>مذكور في مزايا المؤسسات وغير مبني</t>
+        </is>
+      </c>
+      <c r="E17" s="27" t="inlineStr">
+        <is>
+          <t>مطلب مؤسسي متكرّر — يبقى حبراً على ورق حتى يُبنى.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="54" customHeight="1">
+      <c r="A18" s="25" t="inlineStr">
+        <is>
+          <t>تطبيق جوال</t>
+        </is>
+      </c>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>غير ظاهر</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="inlineStr">
+        <is>
+          <t>تطبيق على كل الباقات بما فيها Starter</t>
+        </is>
+      </c>
+      <c r="D18" s="30" t="inlineStr">
+        <is>
+          <t>غير موجود</t>
+        </is>
+      </c>
+      <c r="E18" s="27" t="inlineStr">
+        <is>
+          <t>معروض في ملفك على ثلاث باقات ولا أثر له — إما يُبنى أو يُشطب.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="54" customHeight="1">
+      <c r="A19" s="25" t="inlineStr">
+        <is>
+          <t>ما نتفوّق به</t>
+        </is>
+      </c>
+      <c r="B19" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D19" s="31" t="inlineStr">
+        <is>
+          <t>اللهجات العربية · سلة وزد · واجهة عربية أصلية · أسعار أقل بكثير (19$ مقابل 79$)</t>
+        </is>
+      </c>
+      <c r="E19" s="27" t="inlineStr">
+        <is>
+          <t>هذه نقاط البيع. respond.io تبدأ من 79$ ونحن من 19$ — الفجوة السعرية وحدها رسالة تسويقية.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>أسعارهم للمقارنة — BEON: من 1,199 ج.م إلى 12,399 ج.م شهرياً · respond.io: Starter 79$ · Growth 159$ · Advanced 279–349$ · نحن: 19$ إلى 249$</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A21:E21"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/Qhub - مصفوفة الباقات والمزايا.xlsx
+++ b/docs/Qhub - مصفوفة الباقات والمزايا.xlsx
@@ -907,8 +907,10 @@
       <c r="E12" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="F12" s="8" t="n">
-        <v>249</v>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>بالتواصل</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
@@ -934,9 +936,10 @@
         <f>E12*12*0.8</f>
         <v/>
       </c>
-      <c r="F13" s="8">
-        <f>F12*12*0.8</f>
-        <v/>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>بالتواصل</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -4496,27 +4499,27 @@
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
+          <t>19 / 49 / 99 — والمؤسسات «بالطلب»</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>#REF! — صيغ مكسورة</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
           <t>19 / 49 / 99 / 249</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
-        <is>
-          <t>#REF! — صيغ مكسورة</t>
-        </is>
-      </c>
-      <c r="D7" s="22" t="inlineStr">
-        <is>
-          <t>19 / 49 / 99 / 249</t>
-        </is>
-      </c>
       <c r="E7" s="21" t="inlineStr">
         <is>
-          <t>19 / 49 / 99 / 249</t>
+          <t>19 / 49 / 99 / بالتواصل</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
-          <t>لا شيء — الموقع والنظام متطابقان</t>
+          <t>الثلاث الأولى متطابقة. أما 249 فرقم قائم في الكود في الملفين ولا يراه أي عميل: contactOnly على الموقع يخفيه ويعرض «بالطلب». يُحذف من النظام أو يُحوَّل لسعر أساس داخلي يبني عليه فريق المبيعات.</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4723,7 @@
       </c>
       <c r="B14" s="22" t="inlineStr">
         <is>
-          <t>بالتواصل — السعر يُتّفق عليه</t>
+          <t>contactOnly — تعرض «بالطلب» ولا تعرض رقماً</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -4730,7 +4733,7 @@
       </c>
       <c r="D14" s="22" t="inlineStr">
         <is>
-          <t>سعر معروض 249$ واشتراك ذاتي</t>
+          <t>تُعامَل كباقة عادية: 249$ ظاهرة في /subscribe وزر اشتراك ذاتي</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -4740,7 +4743,7 @@
       </c>
       <c r="F14" s="23" t="inlineStr">
         <is>
-          <t>قرار تجاري: يُعرض السعر أم يبقى «تواصل معنا»؟</t>
+          <t>خلل فعلي: الموقع يقول «تواصل معنا» واللوحة تعرض السعر وتتيح الشراء المباشر. توحيد السلوك — لا اشتراك ذاتي على المؤسسات.</t>
         </is>
       </c>
     </row>
@@ -4759,7 +4762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4870,17 +4873,17 @@
       </c>
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>الموقع يعرض حدّاً محذوفاً</t>
+          <t>المؤسسات تُباع ذاتياً رغم أنها «بالطلب»</t>
         </is>
       </c>
       <c r="C8" s="26" t="inlineStr">
         <is>
-          <t>جدول المقارنة في pricing.ts فيه صف «الأقسام: — / 3 / 10 / بلا حد»، وهذا الحدّ أُلغي عندنا عمداً.</t>
+          <t>الموقع يخفي سعرها ويعرض «بالطلب» (contactOnly). اللوحة تعاملها كباقة عادية: 249$ ظاهرة في /subscribe مع زر اشتراك مباشر — تحققت من ذلك بفتح المسار، ويصل فعلاً لشاشة «إتمام الدفع».</t>
         </is>
       </c>
       <c r="D8" s="27" t="inlineStr">
         <is>
-          <t>حذف الصف من الموقع — نحن نَعِد بحدّ لم يعد موجوداً.</t>
+          <t>يناقض مسار طلب الحدود المخصّصة الذي بنيناه. المفروض لا اشتراك ذاتي على المؤسسات — الزر يقود للنموذج لا للدفع.</t>
         </is>
       </c>
     </row>
@@ -4890,17 +4893,17 @@
       </c>
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>تفريغ الرسائل الصوتية غير عامل</t>
+          <t>الموقع يعرض حدّاً محذوفاً</t>
         </is>
       </c>
       <c r="C9" s="26" t="inlineStr">
         <is>
-          <t>الواجهة كاملة، لكن transcribeAudio تُرجع نصاً ثابتاً، ولا شيء في التطبيق يشغّل المسار أصلاً.</t>
+          <t>جدول المقارنة في pricing.ts فيه صف «الأقسام: — / 3 / 10 / بلا حد»، وهذا الحدّ أُلغي عندنا عمداً.</t>
         </is>
       </c>
       <c r="D9" s="27" t="inlineStr">
         <is>
-          <t>يحتاج باكند — مفتاح المزوّد لا يوضع في المتصفح. البند معروض على الموقع اليوم.</t>
+          <t>حذف الصف من الموقع — نحن نَعِد بحدّ لم يعد موجوداً.</t>
         </is>
       </c>
     </row>
@@ -4910,17 +4913,17 @@
       </c>
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>المساعد الذكي كله يعتمد على دالة وهمية</t>
+          <t>تفريغ الرسائل الصوتية غير عامل</t>
         </is>
       </c>
       <c r="C10" s="26" t="inlineStr">
         <is>
-          <t>getAIResponse في utils/ai.ts تُرجع نصاً ثابتاً. كل صفوف «ردود تلقائية» و«اقتراح الرد» و«قراءة الصور» و«قياس الرضا» مفاتيح في الإعدادات بلا منطق خلفها.</t>
+          <t>الواجهة كاملة، لكن transcribeAudio تُرجع نصاً ثابتاً، ولا شيء في التطبيق يشغّل المسار أصلاً.</t>
         </is>
       </c>
       <c r="D10" s="27" t="inlineStr">
         <is>
-          <t>يحتاج باكند. الإعدادات والواجهات جاهزة بالكامل، ينقص الربط.</t>
+          <t>يحتاج باكند — مفتاح المزوّد لا يوضع في المتصفح. البند معروض على الموقع اليوم.</t>
         </is>
       </c>
     </row>
@@ -4930,17 +4933,17 @@
       </c>
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>أربع مزايا بلا أثر في الكود</t>
+          <t>المساعد الذكي كله يعتمد على دالة وهمية</t>
         </is>
       </c>
       <c r="C11" s="26" t="inlineStr">
         <is>
-          <t>توزيع تلقائي متوازن · إرسال تدريجي · سقف رسائل الحملات · اتفاقية SLA. ولا واحدة منها لها سطر واحد.</t>
+          <t>getAIResponse في utils/ai.ts تُرجع نصاً ثابتاً. كل صفوف «ردود تلقائية» و«اقتراح الرد» و«قراءة الصور» و«قياس الرضا» مفاتيح في الإعدادات بلا منطق خلفها.</t>
         </is>
       </c>
       <c r="D11" s="27" t="inlineStr">
         <is>
-          <t>إما تُبنى أو تُشطب من العرض. اثنتان منها معروضتان على الموقع اليوم.</t>
+          <t>يحتاج باكند. الإعدادات والواجهات جاهزة بالكامل، ينقص الربط.</t>
         </is>
       </c>
     </row>
@@ -4950,17 +4953,17 @@
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>بنود تُضبط ولا تُنفَّذ</t>
+          <t>أربع مزايا بلا أثر في الكود</t>
         </is>
       </c>
       <c r="C12" s="26" t="inlineStr">
         <is>
-          <t>هدف زمن الاستجابة يُحفظ على القسم ولا تنبيه يُطلَق · كلمات التوجيه routingKeywords تُحفظ ولا كود يقرأها · سجلّ الإجراءات على مستوى المحادثة لا الموظف.</t>
+          <t>توزيع تلقائي متوازن · إرسال تدريجي · سقف رسائل الحملات · اتفاقية SLA. ولا واحدة منها لها سطر واحد.</t>
         </is>
       </c>
       <c r="D12" s="27" t="inlineStr">
         <is>
-          <t>ثلاثة بنود قريبة الإنجاز — الحقول موجودة، ينقص المنطق.</t>
+          <t>إما تُبنى أو تُشطب من العرض. اثنتان منها معروضتان على الموقع اليوم.</t>
         </is>
       </c>
     </row>
@@ -4970,17 +4973,17 @@
       </c>
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>بوابة الدفع غير منفّذة</t>
+          <t>بنود تُضبط ولا تُنفَّذ</t>
         </is>
       </c>
       <c r="C13" s="26" t="inlineStr">
         <is>
-          <t>إعدادات Paymob ومفاتيحها موجودة، لكن زر «الانتقال للدفع» يصل لشاشة الدفع ولا يُحصّل شيئاً.</t>
+          <t>هدف زمن الاستجابة يُحفظ على القسم ولا تنبيه يُطلَق · كلمات التوجيه routingKeywords تُحفظ ولا كود يقرأها · سجلّ الإجراءات على مستوى المحادثة لا الموظف.</t>
         </is>
       </c>
       <c r="D13" s="27" t="inlineStr">
         <is>
-          <t>يحتاج باكند. لا يظهر في المصفوفة لأنه واحد في كل الباقات.</t>
+          <t>ثلاثة بنود قريبة الإنجاز — الحقول موجودة، ينقص المنطق.</t>
         </is>
       </c>
     </row>
@@ -4990,17 +4993,17 @@
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>الأمان في وضع عرض</t>
+          <t>بوابة الدفع غير منفّذة</t>
         </is>
       </c>
       <c r="C14" s="26" t="inlineStr">
         <is>
-          <t>التحقق بخطوتين يعمل في المتصفح بسرّ مشترك · رمز OTP يظهر في لافتة على الشاشة · دخول Google و Apple شاشة محاكاة بلا OAuth.</t>
+          <t>إعدادات Paymob ومفاتيحها موجودة، لكن زر «الانتقال للدفع» يصل لشاشة الدفع ولا يُحصّل شيئاً.</t>
         </is>
       </c>
       <c r="D14" s="27" t="inlineStr">
         <is>
-          <t>لا يُطرح للعملاء قبل الباكند. التحقق بخطوتين وحده مذكور في المصفوفة لأنه يختلف بين الباقات.</t>
+          <t>يحتاج باكند. لا يظهر في المصفوفة لأنه واحد في كل الباقات.</t>
         </is>
       </c>
     </row>
@@ -5010,17 +5013,17 @@
       </c>
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>التجربة المجانية: 7 أيام أم 14؟</t>
+          <t>الأمان في وضع عرض</t>
         </is>
       </c>
       <c r="C15" s="26" t="inlineStr">
         <is>
-          <t>صفحة الأسعار تَعِد بـ«7 أيام مجاناً دون بطاقة». النظام يعرف الحالة التجريبية (ClientStatus «trial» و trialEndsAt)، لكن الأدمن وحده يفتحها يدوياً من شاشة العملاء — و**بمدة 14 يوماً** لا 7. التسجيل الذاتي لا ينشئ تجربة إطلاقاً، ولا شيء ينهيها عند انقضائها.</t>
+          <t>التحقق بخطوتين يعمل في المتصفح بسرّ مشترك · رمز OTP يظهر في لافتة على الشاشة · دخول Google و Apple شاشة محاكاة بلا OAuth.</t>
         </is>
       </c>
       <c r="D15" s="27" t="inlineStr">
         <is>
-          <t>ثلاثة قرارات: توحيد المدة (7 أم 14)، وبدء التجربة تلقائياً عند التسجيل، وما الذي يحدث عند انتهائها.</t>
+          <t>لا يُطرح للعملاء قبل الباكند. التحقق بخطوتين وحده مذكور في المصفوفة لأنه يختلف بين الباقات.</t>
         </is>
       </c>
     </row>
@@ -5030,15 +5033,35 @@
       </c>
       <c r="B16" s="25" t="inlineStr">
         <is>
+          <t>التجربة المجانية: 7 أيام أم 14؟</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>صفحة الأسعار تَعِد بـ«7 أيام مجاناً دون بطاقة». النظام يعرف الحالة التجريبية (ClientStatus «trial» و trialEndsAt)، لكن الأدمن وحده يفتحها يدوياً من شاشة العملاء — و**بمدة 14 يوماً** لا 7. التسجيل الذاتي لا ينشئ تجربة إطلاقاً، ولا شيء ينهيها عند انقضائها.</t>
+        </is>
+      </c>
+      <c r="D16" s="27" t="inlineStr">
+        <is>
+          <t>ثلاثة قرارات: توحيد المدة (7 أم 14)، وبدء التجربة تلقائياً عند التسجيل، وما الذي يحدث عند انتهائها.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="A17" s="28" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="25" t="inlineStr">
+        <is>
           <t>مزايا مبنية وغير معروضة</t>
         </is>
       </c>
-      <c r="C16" s="26" t="inlineStr">
+      <c r="C17" s="26" t="inlineStr">
         <is>
           <t>الرسائل الصوتية · تعديل الرسالة خلال 30 دقيقة · فهرسة دورات المحادثة · حالة متاح ومشغول · تصدير التقارير.</t>
         </is>
       </c>
-      <c r="D16" s="27" t="inlineStr">
+      <c r="D17" s="27" t="inlineStr">
         <is>
           <t>أُضيفت للمصفوفة. يستحق بعضها الظهور على الموقع — قرار تسويقي.</t>
         </is>

--- a/docs/Qhub - مصفوفة الباقات والمزايا.xlsx
+++ b/docs/Qhub - مصفوفة الباقات والمزايا.xlsx
@@ -3210,7 +3210,7 @@
       </c>
       <c r="C52" s="13" t="inlineStr">
         <is>
-          <t>يرسل على دفعات لحماية رقمك من الحظر</t>
+          <t>فترة بين كل رسالة وأخرى لحماية رقمك من الحظر</t>
         </is>
       </c>
       <c r="D52" s="18" t="inlineStr">
@@ -3233,14 +3233,14 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="H52" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I52" s="17" t="inlineStr">
-        <is>
-          <t>❌ غير منفّذ</t>
+      <c r="H52" s="15" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="I52" s="16" t="inlineStr">
+        <is>
+          <t>⚠️ جزئي</t>
         </is>
       </c>
     </row>
@@ -4762,7 +4762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4953,17 +4953,17 @@
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>أربع مزايا بلا أثر في الكود</t>
+          <t>الإرسال التدريجي يُضبط ثم يُرمى</t>
         </is>
       </c>
       <c r="C12" s="26" t="inlineStr">
         <is>
-          <t>توزيع تلقائي متوازن · إرسال تدريجي · سقف رسائل الحملات · اتفاقية SLA. ولا واحدة منها لها سطر واحد.</t>
+          <t>الواجهة مبنية بالكامل: أربع سرعات جاهزة (سريع 5-15ث · معتدل 15-45ث · حذر 30-90ث · آمن جداً 60-180ث)، ومؤشّر خطر، وتقدير لمدة الحملة، والقوالب تحمل سرعتها الافتراضية. لكن النوع Campaign ما فيه minDelay ولا maxDelay — الإعداد يعيش في نموذج الإنشاء ويضيع عند الحفظ.</t>
         </is>
       </c>
       <c r="D12" s="27" t="inlineStr">
         <is>
-          <t>إما تُبنى أو تُشطب من العرض. اثنتان منها معروضتان على الموقع اليوم.</t>
+          <t>أقرب بند للإنجاز في الملف كله: حقلان على النوع وحفظهما. الشغل الصعب (الواجهة والسرعات والمؤشّر) خلصان.</t>
         </is>
       </c>
     </row>
@@ -4973,17 +4973,17 @@
       </c>
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>بنود تُضبط ولا تُنفَّذ</t>
+          <t>ثلاث مزايا بلا أثر في الكود</t>
         </is>
       </c>
       <c r="C13" s="26" t="inlineStr">
         <is>
-          <t>هدف زمن الاستجابة يُحفظ على القسم ولا تنبيه يُطلَق · كلمات التوجيه routingKeywords تُحفظ ولا كود يقرأها · سجلّ الإجراءات على مستوى المحادثة لا الموظف.</t>
+          <t>توزيع تلقائي متوازن · سقف رسائل الحملات · اتفاقية SLA. ولا واحدة منها لها سطر واحد. والأسوأ: مقال في قاعدة المعرفة يشرح للعميل أن التوزيع يتم «بنظام Round Robin» — وهو غير مبني.</t>
         </is>
       </c>
       <c r="D13" s="27" t="inlineStr">
         <is>
-          <t>ثلاثة بنود قريبة الإنجاز — الحقول موجودة، ينقص المنطق.</t>
+          <t>إما تُبنى أو تُشطب. وعلى الأقل يُصحَّح مقال قاعدة المعرفة فوراً.</t>
         </is>
       </c>
     </row>
@@ -4993,17 +4993,17 @@
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>بوابة الدفع غير منفّذة</t>
+          <t>بنود تُضبط ولا تُنفَّذ</t>
         </is>
       </c>
       <c r="C14" s="26" t="inlineStr">
         <is>
-          <t>إعدادات Paymob ومفاتيحها موجودة، لكن زر «الانتقال للدفع» يصل لشاشة الدفع ولا يُحصّل شيئاً.</t>
+          <t>هدف زمن الاستجابة يُحفظ على القسم ولا تنبيه يُطلَق · كلمات التوجيه routingKeywords تُحفظ ولا كود يقرأها · سجلّ الإجراءات على مستوى المحادثة لا الموظف.</t>
         </is>
       </c>
       <c r="D14" s="27" t="inlineStr">
         <is>
-          <t>يحتاج باكند. لا يظهر في المصفوفة لأنه واحد في كل الباقات.</t>
+          <t>ثلاثة بنود قريبة الإنجاز — الحقول موجودة، ينقص المنطق.</t>
         </is>
       </c>
     </row>
@@ -5013,17 +5013,17 @@
       </c>
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>الأمان في وضع عرض</t>
+          <t>بوابة الدفع غير منفّذة</t>
         </is>
       </c>
       <c r="C15" s="26" t="inlineStr">
         <is>
-          <t>التحقق بخطوتين يعمل في المتصفح بسرّ مشترك · رمز OTP يظهر في لافتة على الشاشة · دخول Google و Apple شاشة محاكاة بلا OAuth.</t>
+          <t>إعدادات Paymob ومفاتيحها موجودة، لكن زر «الانتقال للدفع» يصل لشاشة الدفع ولا يُحصّل شيئاً.</t>
         </is>
       </c>
       <c r="D15" s="27" t="inlineStr">
         <is>
-          <t>لا يُطرح للعملاء قبل الباكند. التحقق بخطوتين وحده مذكور في المصفوفة لأنه يختلف بين الباقات.</t>
+          <t>يحتاج باكند. لا يظهر في المصفوفة لأنه واحد في كل الباقات.</t>
         </is>
       </c>
     </row>
@@ -5033,17 +5033,17 @@
       </c>
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>التجربة المجانية: 7 أيام أم 14؟</t>
+          <t>الأمان في وضع عرض</t>
         </is>
       </c>
       <c r="C16" s="26" t="inlineStr">
         <is>
-          <t>صفحة الأسعار تَعِد بـ«7 أيام مجاناً دون بطاقة». النظام يعرف الحالة التجريبية (ClientStatus «trial» و trialEndsAt)، لكن الأدمن وحده يفتحها يدوياً من شاشة العملاء — و**بمدة 14 يوماً** لا 7. التسجيل الذاتي لا ينشئ تجربة إطلاقاً، ولا شيء ينهيها عند انقضائها.</t>
+          <t>التحقق بخطوتين يعمل في المتصفح بسرّ مشترك · رمز OTP يظهر في لافتة على الشاشة · دخول Google و Apple شاشة محاكاة بلا OAuth.</t>
         </is>
       </c>
       <c r="D16" s="27" t="inlineStr">
         <is>
-          <t>ثلاثة قرارات: توحيد المدة (7 أم 14)، وبدء التجربة تلقائياً عند التسجيل، وما الذي يحدث عند انتهائها.</t>
+          <t>لا يُطرح للعملاء قبل الباكند. التحقق بخطوتين وحده مذكور في المصفوفة لأنه يختلف بين الباقات.</t>
         </is>
       </c>
     </row>
@@ -5053,15 +5053,35 @@
       </c>
       <c r="B17" s="25" t="inlineStr">
         <is>
+          <t>التجربة المجانية: 7 أيام أم 14؟</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>صفحة الأسعار تَعِد بـ«7 أيام مجاناً دون بطاقة». النظام يعرف الحالة التجريبية (ClientStatus «trial» و trialEndsAt)، لكن الأدمن وحده يفتحها يدوياً من شاشة العملاء — و**بمدة 14 يوماً** لا 7. التسجيل الذاتي لا ينشئ تجربة إطلاقاً، ولا شيء ينهيها عند انقضائها.</t>
+        </is>
+      </c>
+      <c r="D17" s="27" t="inlineStr">
+        <is>
+          <t>ثلاثة قرارات: توحيد المدة (7 أم 14)، وبدء التجربة تلقائياً عند التسجيل، وما الذي يحدث عند انتهائها.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="56" customHeight="1">
+      <c r="A18" s="28" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="25" t="inlineStr">
+        <is>
           <t>مزايا مبنية وغير معروضة</t>
         </is>
       </c>
-      <c r="C17" s="26" t="inlineStr">
+      <c r="C18" s="26" t="inlineStr">
         <is>
           <t>الرسائل الصوتية · تعديل الرسالة خلال 30 دقيقة · فهرسة دورات المحادثة · حالة متاح ومشغول · تصدير التقارير.</t>
         </is>
       </c>
-      <c r="D17" s="27" t="inlineStr">
+      <c r="D18" s="27" t="inlineStr">
         <is>
           <t>أُضيفت للمصفوفة. يستحق بعضها الظهور على الموقع — قرار تسويقي.</t>
         </is>

--- a/docs/Qhub - مصفوفة الباقات والمزايا.xlsx
+++ b/docs/Qhub - مصفوفة الباقات والمزايا.xlsx
@@ -1113,7 +1113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2196,57 +2196,57 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>صندوق الوارد</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>تطبيق الموظفين على الجوال</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>فريقك يرد من جواله: المحادثات والتحويل والرسائل الصوتية وحالة متاح/مشغول</t>
+        </is>
+      </c>
+      <c r="D29" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E29" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F29" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G29" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H29" s="15" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="I29" s="21" t="inlineStr">
+        <is>
+          <t>✅ منفّذ</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>المساعد الذكي</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>المساعد الذكي</t>
-        </is>
-      </c>
-      <c r="B30" s="12" t="inlineStr">
-        <is>
-          <t>ردود تلقائية على مدار الساعة</t>
-        </is>
-      </c>
-      <c r="C30" s="13" t="inlineStr">
-        <is>
-          <t>يرد على عملائك حتى خارج الدوام</t>
-        </is>
-      </c>
-      <c r="D30" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E30" s="19" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F30" s="19" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G30" s="19" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H30" s="15" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="I30" s="16" t="inlineStr">
-        <is>
-          <t>⚠️ جزئي</t>
         </is>
       </c>
     </row>
@@ -2258,12 +2258,12 @@
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>يفهم اللغات واللهجات</t>
+          <t>ردود تلقائية على مدار الساعة</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>يفهم العربية بلهجاتها ويرد بنفس اللهجة</t>
+          <t>يرد على عملائك حتى خارج الدوام</t>
         </is>
       </c>
       <c r="D31" s="18" t="inlineStr">
@@ -2291,9 +2291,9 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="I31" s="21" t="inlineStr">
-        <is>
-          <t>✅ منفّذ</t>
+      <c r="I31" s="16" t="inlineStr">
+        <is>
+          <t>⚠️ جزئي</t>
         </is>
       </c>
     </row>
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>قاعدة معرفة مخصّصة</t>
+          <t>يفهم اللغات واللهجات</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>ترفع منتجاتك وأسعارك وسياساتك فيرد منها لا بالتخمين</t>
+          <t>يفهم العربية بلهجاتها ويرد بنفس اللهجة</t>
         </is>
       </c>
       <c r="D32" s="18" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>أسلوب الرد</t>
+          <t>قاعدة معرفة مخصّصة</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
         <is>
-          <t>تحدّد أسلوبه: رسمي أو ودود أو مختصر، باسم علامتك</t>
+          <t>ترفع منتجاتك وأسعارك وسياساتك فيرد منها لا بالتخمين</t>
         </is>
       </c>
       <c r="D33" s="18" t="inlineStr">
@@ -2399,12 +2399,12 @@
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>تحويل للموظف عند الحاجة</t>
+          <t>أسلوب الرد</t>
         </is>
       </c>
       <c r="C34" s="13" t="inlineStr">
         <is>
-          <t>يحوّل المحادثة للموظف المناسب ومعها ملخّص جاهز</t>
+          <t>تحدّد أسلوبه: رسمي أو ودود أو مختصر، باسم علامتك</t>
         </is>
       </c>
       <c r="D34" s="18" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>مواضيع لا يتكلم فيها</t>
+          <t>تحويل للموظف عند الحاجة</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr">
         <is>
-          <t>تحدّد مواضيع حسّاسة يمتنع عنها ويحوّلها للفريق</t>
+          <t>يحوّل المحادثة للموظف المناسب ومعها ملخّص جاهز</t>
         </is>
       </c>
       <c r="D35" s="18" t="inlineStr">
@@ -2474,9 +2474,9 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="H35" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="H35" s="15" t="inlineStr">
+        <is>
+          <t>✔</t>
         </is>
       </c>
       <c r="I35" s="21" t="inlineStr">
@@ -2493,12 +2493,12 @@
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>تحويل فوري بكلمة</t>
+          <t>مواضيع لا يتكلم فيها</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
-          <t>كلمات مثل «موظف» أو «شكوى» تنقل المحادثة للفريق فوراً</t>
+          <t>تحدّد مواضيع حسّاسة يمتنع عنها ويحوّلها للفريق</t>
         </is>
       </c>
       <c r="D36" s="18" t="inlineStr">
@@ -2540,12 +2540,12 @@
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>رصيد الردود الشهري</t>
+          <t>تحويل فوري بكلمة</t>
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>عدد ردود المساعد المشمولة في باقتك</t>
+          <t>كلمات مثل «موظف» أو «شكوى» تنقل المحادثة للفريق فوراً</t>
         </is>
       </c>
       <c r="D37" s="18" t="inlineStr">
@@ -2553,19 +2553,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E37" s="14" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
-      </c>
-      <c r="F37" s="14" t="inlineStr">
-        <is>
-          <t>10,000</t>
-        </is>
-      </c>
-      <c r="G37" s="14" t="inlineStr">
-        <is>
-          <t>مخصّص</t>
+      <c r="E37" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F37" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G37" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
         </is>
       </c>
       <c r="H37" s="20" t="inlineStr">
@@ -2573,9 +2573,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I37" s="16" t="inlineStr">
-        <is>
-          <t>⚠️ جزئي</t>
+      <c r="I37" s="21" t="inlineStr">
+        <is>
+          <t>✅ منفّذ</t>
         </is>
       </c>
     </row>
@@ -2587,12 +2587,12 @@
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>إعدادات مستقلة لكل قناة</t>
+          <t>رصيد الردود الشهري</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr">
         <is>
-          <t>نبرة وقواعد مختلفة لكل قناة على حدة</t>
+          <t>عدد ردود المساعد المشمولة في باقتك</t>
         </is>
       </c>
       <c r="D38" s="18" t="inlineStr">
@@ -2600,19 +2600,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E38" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F38" s="19" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G38" s="19" t="inlineStr">
-        <is>
-          <t>✔</t>
+      <c r="E38" s="14" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="F38" s="14" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="G38" s="14" t="inlineStr">
+        <is>
+          <t>مخصّص</t>
         </is>
       </c>
       <c r="H38" s="20" t="inlineStr">
@@ -2620,9 +2620,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I38" s="21" t="inlineStr">
-        <is>
-          <t>✅ منفّذ</t>
+      <c r="I38" s="16" t="inlineStr">
+        <is>
+          <t>⚠️ جزئي</t>
         </is>
       </c>
     </row>
@@ -2634,12 +2634,12 @@
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>تفريغ الرسائل الصوتية</t>
+          <t>إعدادات مستقلة لكل قناة</t>
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>يحوّل الرسالة الصوتية إلى نص تقرأه وتبحث فيه</t>
+          <t>نبرة وقواعد مختلفة لكل قناة على حدة</t>
         </is>
       </c>
       <c r="D39" s="18" t="inlineStr">
@@ -2662,14 +2662,14 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="H39" s="15" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="I39" s="16" t="inlineStr">
-        <is>
-          <t>⚠️ جزئي</t>
+      <c r="H39" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I39" s="21" t="inlineStr">
+        <is>
+          <t>✅ منفّذ</t>
         </is>
       </c>
     </row>
@@ -2681,12 +2681,12 @@
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>قراءة الصور والملفات</t>
+          <t>تفريغ الرسائل الصوتية</t>
         </is>
       </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
-          <t>يفهم الصورة أو ملف PDF الذي يرسله العميل</t>
+          <t>يحوّل الرسالة الصوتية إلى نص تقرأه وتبحث فيه</t>
         </is>
       </c>
       <c r="D40" s="18" t="inlineStr">
@@ -2709,9 +2709,9 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="H40" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="H40" s="15" t="inlineStr">
+        <is>
+          <t>✔</t>
         </is>
       </c>
       <c r="I40" s="16" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>قياس رضا العميل أثناء المحادثة</t>
+          <t>قراءة الصور والملفات</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>ينبّهك لما تكون نبرة العميل سلبية</t>
+          <t>يفهم الصورة أو ملف PDF الذي يرسله العميل</t>
         </is>
       </c>
       <c r="D41" s="18" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>اقتراح الرد على الموظف</t>
+          <t>قياس رضا العميل أثناء المحادثة</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
         <is>
-          <t>يقترح رداً جاهزاً للموظف قبل أن يكتب</t>
+          <t>ينبّهك لما تكون نبرة العميل سلبية</t>
         </is>
       </c>
       <c r="D42" s="18" t="inlineStr">
@@ -2788,9 +2788,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E42" s="19" t="inlineStr">
-        <is>
-          <t>✔</t>
+      <c r="E42" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F42" s="19" t="inlineStr">
@@ -2822,96 +2822,96 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
+          <t>اقتراح الرد على الموظف</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="inlineStr">
+        <is>
+          <t>يقترح رداً جاهزاً للموظف قبل أن يكتب</t>
+        </is>
+      </c>
+      <c r="D43" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E43" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F43" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G43" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H43" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I43" s="16" t="inlineStr">
+        <is>
+          <t>⚠️ جزئي</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>المساعد الذكي</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
           <t>يتعلّم من ردود فريقك</t>
         </is>
       </c>
-      <c r="C43" s="13" t="inlineStr">
+      <c r="C44" s="13" t="inlineStr">
         <is>
           <t>يتحسّن مع الوقت من أسلوب ردود موظفيك</t>
         </is>
       </c>
-      <c r="D43" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E43" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F43" s="19" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G43" s="19" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H43" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I43" s="16" t="inlineStr">
+      <c r="D44" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E44" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F44" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G44" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H44" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I44" s="16" t="inlineStr">
         <is>
           <t>⚠️ جزئي</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="11" t="inlineStr">
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>التسويق والحملات</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="26" customHeight="1">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>التسويق والحملات</t>
-        </is>
-      </c>
-      <c r="B45" s="12" t="inlineStr">
-        <is>
-          <t>حملات واتساب</t>
-        </is>
-      </c>
-      <c r="C45" s="13" t="inlineStr">
-        <is>
-          <t>ترسل عرضاً أو إعلاناً لقائمة عملائك على واتساب</t>
-        </is>
-      </c>
-      <c r="D45" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E45" s="19" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F45" s="19" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G45" s="19" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H45" s="15" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="I45" s="21" t="inlineStr">
-        <is>
-          <t>✅ منفّذ</t>
         </is>
       </c>
     </row>
@@ -2923,12 +2923,12 @@
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>حملات بريد إلكتروني</t>
+          <t>حملات واتساب</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
-          <t>نفس الشيء عبر البريد</t>
+          <t>ترسل عرضاً أو إعلاناً لقائمة عملائك على واتساب</t>
         </is>
       </c>
       <c r="D46" s="18" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>قوالب جاهزة</t>
+          <t>حملات بريد إلكتروني</t>
         </is>
       </c>
       <c r="C47" s="13" t="inlineStr">
         <is>
-          <t>قوالب رسائل تعدّلها بدل الكتابة من الصفر</t>
+          <t>نفس الشيء عبر البريد</t>
         </is>
       </c>
       <c r="D47" s="18" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>استهداف بالوسوم</t>
+          <t>قوالب جاهزة</t>
         </is>
       </c>
       <c r="C48" s="13" t="inlineStr">
         <is>
-          <t>ترسل الحملة لفئة محدّدة من عملائك لا للكل</t>
+          <t>قوالب رسائل تعدّلها بدل الكتابة من الصفر</t>
         </is>
       </c>
       <c r="D48" s="18" t="inlineStr">
@@ -3045,9 +3045,9 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="H48" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="H48" s="15" t="inlineStr">
+        <is>
+          <t>✔</t>
         </is>
       </c>
       <c r="I48" s="21" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>تقارير الحملات</t>
+          <t>استهداف بالوسوم</t>
         </is>
       </c>
       <c r="C49" s="13" t="inlineStr">
         <is>
-          <t>كم وصلت وكم فُتحت وكم ردّوا</t>
+          <t>ترسل الحملة لفئة محدّدة من عملائك لا للكل</t>
         </is>
       </c>
       <c r="D49" s="18" t="inlineStr">
@@ -3092,9 +3092,9 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="H49" s="15" t="inlineStr">
-        <is>
-          <t>✔</t>
+      <c r="H49" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I49" s="21" t="inlineStr">
@@ -3111,12 +3111,12 @@
       </c>
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>جدولة الإرسال</t>
+          <t>تقارير الحملات</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
         <is>
-          <t>تحدّد وقت الإرسال مسبقاً</t>
+          <t>كم وصلت وكم فُتحت وكم ردّوا</t>
         </is>
       </c>
       <c r="D50" s="18" t="inlineStr">
@@ -3124,9 +3124,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E50" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="E50" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
         </is>
       </c>
       <c r="F50" s="19" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>عدد رسائل الحملات شهرياً</t>
+          <t>جدولة الإرسال</t>
         </is>
       </c>
       <c r="C51" s="13" t="inlineStr">
         <is>
-          <t>سقف رسائل الحملات المشمولة — رسوم Meta منفصلة</t>
+          <t>تحدّد وقت الإرسال مسبقاً</t>
         </is>
       </c>
       <c r="D51" s="18" t="inlineStr">
@@ -3171,29 +3171,29 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E51" s="14" t="inlineStr">
-        <is>
-          <t>1,000</t>
-        </is>
-      </c>
-      <c r="F51" s="14" t="inlineStr">
-        <is>
-          <t>10,000</t>
-        </is>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>مخصّص</t>
-        </is>
-      </c>
-      <c r="H51" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I51" s="17" t="inlineStr">
-        <is>
-          <t>❌ غير منفّذ</t>
+      <c r="E51" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F51" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G51" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H51" s="15" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="I51" s="21" t="inlineStr">
+        <is>
+          <t>✅ منفّذ</t>
         </is>
       </c>
     </row>
@@ -3205,96 +3205,96 @@
       </c>
       <c r="B52" s="12" t="inlineStr">
         <is>
+          <t>عدد رسائل الحملات شهرياً</t>
+        </is>
+      </c>
+      <c r="C52" s="13" t="inlineStr">
+        <is>
+          <t>سقف رسائل الحملات المشمولة — رسوم Meta منفصلة</t>
+        </is>
+      </c>
+      <c r="D52" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E52" s="14" t="inlineStr">
+        <is>
+          <t>1,000</t>
+        </is>
+      </c>
+      <c r="F52" s="14" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="G52" s="14" t="inlineStr">
+        <is>
+          <t>مخصّص</t>
+        </is>
+      </c>
+      <c r="H52" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I52" s="17" t="inlineStr">
+        <is>
+          <t>❌ غير منفّذ</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="26" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>التسويق والحملات</t>
+        </is>
+      </c>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
           <t>إرسال تدريجي</t>
         </is>
       </c>
-      <c r="C52" s="13" t="inlineStr">
+      <c r="C53" s="13" t="inlineStr">
         <is>
           <t>فترة بين كل رسالة وأخرى لحماية رقمك من الحظر</t>
         </is>
       </c>
-      <c r="D52" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E52" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F52" s="19" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G52" s="19" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H52" s="15" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="I52" s="16" t="inlineStr">
+      <c r="D53" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E53" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F53" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G53" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H53" s="15" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="I53" s="16" t="inlineStr">
         <is>
           <t>⚠️ جزئي</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="11" t="inlineStr">
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="11" t="inlineStr">
         <is>
           <t>الفريق والصلاحيات</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="26" customHeight="1">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>الفريق والصلاحيات</t>
-        </is>
-      </c>
-      <c r="B54" s="12" t="inlineStr">
-        <is>
-          <t>أدوار وصلاحيات</t>
-        </is>
-      </c>
-      <c r="C54" s="13" t="inlineStr">
-        <is>
-          <t>تحدّد ما يشوفه وما يعمله كل موظف</t>
-        </is>
-      </c>
-      <c r="D54" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E54" s="19" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F54" s="19" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G54" s="19" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H54" s="15" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="I54" s="21" t="inlineStr">
-        <is>
-          <t>✅ منفّذ</t>
         </is>
       </c>
     </row>
@@ -3306,12 +3306,12 @@
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>ساعات عمل ورد خارج الدوام</t>
+          <t>أدوار وصلاحيات</t>
         </is>
       </c>
       <c r="C55" s="13" t="inlineStr">
         <is>
-          <t>رسالة تلقائية خارج أوقات عملكم</t>
+          <t>تحدّد ما يشوفه وما يعمله كل موظف</t>
         </is>
       </c>
       <c r="D55" s="18" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="B56" s="12" t="inlineStr">
         <is>
-          <t>حالة متاح ومشغول</t>
+          <t>ساعات عمل ورد خارج الدوام</t>
         </is>
       </c>
       <c r="C56" s="13" t="inlineStr">
         <is>
-          <t>الموظف يعلن حالته فلا تصله محادثات وهو مشغول</t>
+          <t>رسالة تلقائية خارج أوقات عملكم</t>
         </is>
       </c>
       <c r="D56" s="18" t="inlineStr">
@@ -3381,9 +3381,9 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="H56" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="H56" s="15" t="inlineStr">
+        <is>
+          <t>✔</t>
         </is>
       </c>
       <c r="I56" s="21" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>هدف زمن الاستجابة لكل قسم</t>
+          <t>حالة متاح ومشغول</t>
         </is>
       </c>
       <c r="C57" s="13" t="inlineStr">
         <is>
-          <t>تحدّد خلال كم دقيقة يجب أن يصل أول رد</t>
+          <t>الموظف يعلن حالته فلا تصله محادثات وهو مشغول</t>
         </is>
       </c>
       <c r="D57" s="18" t="inlineStr">
@@ -3413,9 +3413,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E57" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="E57" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
         </is>
       </c>
       <c r="F57" s="19" t="inlineStr">
@@ -3433,9 +3433,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I57" s="16" t="inlineStr">
-        <is>
-          <t>⚠️ جزئي</t>
+      <c r="I57" s="21" t="inlineStr">
+        <is>
+          <t>✅ منفّذ</t>
         </is>
       </c>
     </row>
@@ -3447,12 +3447,12 @@
       </c>
       <c r="B58" s="12" t="inlineStr">
         <is>
-          <t>توزيع بكلمة مفتاحية</t>
+          <t>هدف زمن الاستجابة لكل قسم</t>
         </is>
       </c>
       <c r="C58" s="13" t="inlineStr">
         <is>
-          <t>محادثة فيها كلمة «فاتورة» تروح لقسم المحاسبة</t>
+          <t>تحدّد خلال كم دقيقة يجب أن يصل أول رد</t>
         </is>
       </c>
       <c r="D58" s="18" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>سجلّ إجراءات الموظفين</t>
+          <t>توزيع بكلمة مفتاحية</t>
         </is>
       </c>
       <c r="C59" s="13" t="inlineStr">
         <is>
-          <t>تشوف من فتح ومن ردّ ومن أغلق</t>
+          <t>محادثة فيها كلمة «فاتورة» تروح لقسم المحاسبة</t>
         </is>
       </c>
       <c r="D59" s="18" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="B60" s="12" t="inlineStr">
         <is>
-          <t>توزيع تلقائي متوازن</t>
+          <t>سجلّ إجراءات الموظفين</t>
         </is>
       </c>
       <c r="C60" s="13" t="inlineStr">
         <is>
-          <t>المحادثات تتوزّع على الفريق بالتساوي</t>
+          <t>تشوف من فتح ومن ردّ ومن أغلق</t>
         </is>
       </c>
       <c r="D60" s="18" t="inlineStr">
@@ -3554,9 +3554,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E60" s="19" t="inlineStr">
-        <is>
-          <t>✔</t>
+      <c r="E60" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F60" s="19" t="inlineStr">
@@ -3574,9 +3574,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I60" s="17" t="inlineStr">
-        <is>
-          <t>❌ غير منفّذ</t>
+      <c r="I60" s="16" t="inlineStr">
+        <is>
+          <t>⚠️ جزئي</t>
         </is>
       </c>
     </row>
@@ -3588,96 +3588,96 @@
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
+          <t>توزيع تلقائي متوازن</t>
+        </is>
+      </c>
+      <c r="C61" s="13" t="inlineStr">
+        <is>
+          <t>المحادثات تتوزّع على الفريق بالتساوي</t>
+        </is>
+      </c>
+      <c r="D61" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E61" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F61" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G61" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H61" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I61" s="17" t="inlineStr">
+        <is>
+          <t>❌ غير منفّذ</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="26" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>الفريق والصلاحيات</t>
+        </is>
+      </c>
+      <c r="B62" s="12" t="inlineStr">
+        <is>
           <t>التحقق بخطوتين</t>
         </is>
       </c>
-      <c r="C61" s="13" t="inlineStr">
+      <c r="C62" s="13" t="inlineStr">
         <is>
           <t>طبقة حماية ثانية على حسابات فريقك</t>
         </is>
       </c>
-      <c r="D61" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E61" s="19" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F61" s="19" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G61" s="19" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H61" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I61" s="16" t="inlineStr">
+      <c r="D62" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E62" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F62" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G62" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H62" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I62" s="16" t="inlineStr">
         <is>
           <t>⚠️ جزئي</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="22" customHeight="1">
-      <c r="A62" s="11" t="inlineStr">
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="11" t="inlineStr">
         <is>
           <t>العملاء</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="26" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>العملاء</t>
-        </is>
-      </c>
-      <c r="B63" s="12" t="inlineStr">
-        <is>
-          <t>ملف العميل</t>
-        </is>
-      </c>
-      <c r="C63" s="13" t="inlineStr">
-        <is>
-          <t>كل بيانات العميل وسجل محادثاته في مكان واحد</t>
-        </is>
-      </c>
-      <c r="D63" s="19" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E63" s="19" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F63" s="19" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G63" s="19" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H63" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I63" s="21" t="inlineStr">
-        <is>
-          <t>✅ منفّذ</t>
         </is>
       </c>
     </row>
@@ -3689,12 +3689,12 @@
       </c>
       <c r="B64" s="12" t="inlineStr">
         <is>
-          <t>تصنيف العملاء</t>
+          <t>ملف العميل</t>
         </is>
       </c>
       <c r="C64" s="13" t="inlineStr">
         <is>
-          <t>تقسم عملاءك لفئات تتعامل مع كل فئة بطريقة</t>
+          <t>كل بيانات العميل وسجل محادثاته في مكان واحد</t>
         </is>
       </c>
       <c r="D64" s="19" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>قاعدة المعرفة</t>
+          <t>تصنيف العملاء</t>
         </is>
       </c>
       <c r="C65" s="13" t="inlineStr">
         <is>
-          <t>مقالات وأسئلة شائعة يستخدمها فريقك والمساعد</t>
+          <t>تقسم عملاءك لفئات تتعامل مع كل فئة بطريقة</t>
         </is>
       </c>
       <c r="D65" s="19" t="inlineStr">
@@ -3783,17 +3783,17 @@
       </c>
       <c r="B66" s="12" t="inlineStr">
         <is>
-          <t>تقييمات العملاء</t>
+          <t>قاعدة المعرفة</t>
         </is>
       </c>
       <c r="C66" s="13" t="inlineStr">
         <is>
-          <t>يقيّم العميل الخدمة بعد إغلاق المحادثة</t>
-        </is>
-      </c>
-      <c r="D66" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>مقالات وأسئلة شائعة يستخدمها فريقك والمساعد</t>
+        </is>
+      </c>
+      <c r="D66" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
         </is>
       </c>
       <c r="E66" s="19" t="inlineStr">
@@ -3811,9 +3811,9 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="H66" s="15" t="inlineStr">
-        <is>
-          <t>✔</t>
+      <c r="H66" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I66" s="21" t="inlineStr">
@@ -3830,12 +3830,12 @@
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>الشكاوى والاقتراحات</t>
+          <t>تقييمات العملاء</t>
         </is>
       </c>
       <c r="C67" s="13" t="inlineStr">
         <is>
-          <t>صندوق منفصل للشكاوى تتابعه حتى الإغلاق</t>
+          <t>يقيّم العميل الخدمة بعد إغلاق المحادثة</t>
         </is>
       </c>
       <c r="D67" s="18" t="inlineStr">
@@ -3858,9 +3858,9 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="H67" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="H67" s="15" t="inlineStr">
+        <is>
+          <t>✔</t>
         </is>
       </c>
       <c r="I67" s="21" t="inlineStr">
@@ -3877,96 +3877,96 @@
       </c>
       <c r="B68" s="12" t="inlineStr">
         <is>
+          <t>الشكاوى والاقتراحات</t>
+        </is>
+      </c>
+      <c r="C68" s="13" t="inlineStr">
+        <is>
+          <t>صندوق منفصل للشكاوى تتابعه حتى الإغلاق</t>
+        </is>
+      </c>
+      <c r="D68" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E68" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F68" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G68" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H68" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I68" s="21" t="inlineStr">
+        <is>
+          <t>✅ منفّذ</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="26" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>العملاء</t>
+        </is>
+      </c>
+      <c r="B69" s="12" t="inlineStr">
+        <is>
           <t>سجل نشاط العميل</t>
         </is>
       </c>
-      <c r="C68" s="13" t="inlineStr">
+      <c r="C69" s="13" t="inlineStr">
         <is>
           <t>كل ما عمله العميل معك بالترتيب الزمني</t>
         </is>
       </c>
-      <c r="D68" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E68" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F68" s="19" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G68" s="19" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H68" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I68" s="21" t="inlineStr">
+      <c r="D69" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E69" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F69" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G69" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H69" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I69" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="22" customHeight="1">
-      <c r="A69" s="11" t="inlineStr">
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="11" t="inlineStr">
         <is>
           <t>التقارير</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="26" customHeight="1">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>التقارير</t>
-        </is>
-      </c>
-      <c r="B70" s="12" t="inlineStr">
-        <is>
-          <t>تقارير الأداء</t>
-        </is>
-      </c>
-      <c r="C70" s="13" t="inlineStr">
-        <is>
-          <t>لوحة تشوف فيها حجم العمل وأداء الفريق</t>
-        </is>
-      </c>
-      <c r="D70" s="14" t="inlineStr">
-        <is>
-          <t>أساسية</t>
-        </is>
-      </c>
-      <c r="E70" s="14" t="inlineStr">
-        <is>
-          <t>متقدّمة</t>
-        </is>
-      </c>
-      <c r="F70" s="14" t="inlineStr">
-        <is>
-          <t>متقدّمة</t>
-        </is>
-      </c>
-      <c r="G70" s="14" t="inlineStr">
-        <is>
-          <t>متقدّمة</t>
-        </is>
-      </c>
-      <c r="H70" s="15" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="I70" s="21" t="inlineStr">
-        <is>
-          <t>✅ منفّذ</t>
         </is>
       </c>
     </row>
@@ -3978,37 +3978,37 @@
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>متوسط زمن أول رد</t>
+          <t>تقارير الأداء</t>
         </is>
       </c>
       <c r="C71" s="13" t="inlineStr">
         <is>
-          <t>كم يستنى عميلك قبل أول رد</t>
-        </is>
-      </c>
-      <c r="D71" s="19" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E71" s="19" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F71" s="19" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G71" s="19" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H71" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>لوحة تشوف فيها حجم العمل وأداء الفريق</t>
+        </is>
+      </c>
+      <c r="D71" s="14" t="inlineStr">
+        <is>
+          <t>أساسية</t>
+        </is>
+      </c>
+      <c r="E71" s="14" t="inlineStr">
+        <is>
+          <t>متقدّمة</t>
+        </is>
+      </c>
+      <c r="F71" s="14" t="inlineStr">
+        <is>
+          <t>متقدّمة</t>
+        </is>
+      </c>
+      <c r="G71" s="14" t="inlineStr">
+        <is>
+          <t>متقدّمة</t>
+        </is>
+      </c>
+      <c r="H71" s="15" t="inlineStr">
+        <is>
+          <t>✔</t>
         </is>
       </c>
       <c r="I71" s="21" t="inlineStr">
@@ -4025,17 +4025,17 @@
       </c>
       <c r="B72" s="12" t="inlineStr">
         <is>
-          <t>ساعات الذروة</t>
+          <t>متوسط زمن أول رد</t>
         </is>
       </c>
       <c r="C72" s="13" t="inlineStr">
         <is>
-          <t>أي ساعات اليوم أكثر ضغطاً لتوزّع فريقك عليها</t>
-        </is>
-      </c>
-      <c r="D72" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>كم يستنى عميلك قبل أول رد</t>
+        </is>
+      </c>
+      <c r="D72" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
         </is>
       </c>
       <c r="E72" s="19" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>تنبيه عند تأخّر الرد</t>
+          <t>ساعات الذروة</t>
         </is>
       </c>
       <c r="C73" s="13" t="inlineStr">
         <is>
-          <t>ينبّهك لما تتجاوز محادثة الوقت المسموح</t>
+          <t>أي ساعات اليوم أكثر ضغطاً لتوزّع فريقك عليها</t>
         </is>
       </c>
       <c r="D73" s="18" t="inlineStr">
@@ -4085,9 +4085,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E73" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="E73" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
         </is>
       </c>
       <c r="F73" s="19" t="inlineStr">
@@ -4105,9 +4105,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I73" s="16" t="inlineStr">
-        <is>
-          <t>⚠️ جزئي</t>
+      <c r="I73" s="21" t="inlineStr">
+        <is>
+          <t>✅ منفّذ</t>
         </is>
       </c>
     </row>
@@ -4119,96 +4119,96 @@
       </c>
       <c r="B74" s="12" t="inlineStr">
         <is>
+          <t>تنبيه عند تأخّر الرد</t>
+        </is>
+      </c>
+      <c r="C74" s="13" t="inlineStr">
+        <is>
+          <t>ينبّهك لما تتجاوز محادثة الوقت المسموح</t>
+        </is>
+      </c>
+      <c r="D74" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G74" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H74" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="16" t="inlineStr">
+        <is>
+          <t>⚠️ جزئي</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="26" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>التقارير</t>
+        </is>
+      </c>
+      <c r="B75" s="12" t="inlineStr">
+        <is>
           <t>تصدير التقارير</t>
         </is>
       </c>
-      <c r="C74" s="13" t="inlineStr">
+      <c r="C75" s="13" t="inlineStr">
         <is>
           <t>تنزّل تقاريرك ملف CSV</t>
         </is>
       </c>
-      <c r="D74" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="19" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="G74" s="19" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H74" s="15" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="I74" s="21" t="inlineStr">
+      <c r="D75" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E75" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F75" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="G75" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H75" s="15" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="I75" s="21" t="inlineStr">
         <is>
           <t>✅ منفّذ</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="22" customHeight="1">
-      <c r="A75" s="11" t="inlineStr">
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="11" t="inlineStr">
         <is>
           <t>الربط والدعم</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="26" customHeight="1">
-      <c r="A76" s="6" t="inlineStr">
-        <is>
-          <t>الربط والدعم</t>
-        </is>
-      </c>
-      <c r="B76" s="12" t="inlineStr">
-        <is>
-          <t>تكامل API</t>
-        </is>
-      </c>
-      <c r="C76" s="13" t="inlineStr">
-        <is>
-          <t>تربط Qhub بأنظمتك الأخرى</t>
-        </is>
-      </c>
-      <c r="D76" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E76" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F76" s="14" t="inlineStr">
-        <is>
-          <t>محدود</t>
-        </is>
-      </c>
-      <c r="G76" s="14" t="inlineStr">
-        <is>
-          <t>كامل</t>
-        </is>
-      </c>
-      <c r="H76" s="15" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="I76" s="16" t="inlineStr">
-        <is>
-          <t>⚠️ جزئي</t>
         </is>
       </c>
     </row>
@@ -4220,32 +4220,32 @@
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>الدعم</t>
+          <t>تكامل API</t>
         </is>
       </c>
       <c r="C77" s="13" t="inlineStr">
         <is>
-          <t>كيف تتواصل معنا لما تحتاج مساعدة</t>
-        </is>
-      </c>
-      <c r="D77" s="14" t="inlineStr">
-        <is>
-          <t>بريد إلكتروني</t>
-        </is>
-      </c>
-      <c r="E77" s="14" t="inlineStr">
-        <is>
-          <t>أولوية</t>
+          <t>تربط Qhub بأنظمتك الأخرى</t>
+        </is>
+      </c>
+      <c r="D77" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E77" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F77" s="14" t="inlineStr">
         <is>
-          <t>أولوية</t>
+          <t>محدود</t>
         </is>
       </c>
       <c r="G77" s="14" t="inlineStr">
         <is>
-          <t>مدير حساب</t>
+          <t>كامل</t>
         </is>
       </c>
       <c r="H77" s="15" t="inlineStr">
@@ -4267,98 +4267,145 @@
       </c>
       <c r="B78" s="12" t="inlineStr">
         <is>
+          <t>الدعم</t>
+        </is>
+      </c>
+      <c r="C78" s="13" t="inlineStr">
+        <is>
+          <t>كيف تتواصل معنا لما تحتاج مساعدة</t>
+        </is>
+      </c>
+      <c r="D78" s="14" t="inlineStr">
+        <is>
+          <t>بريد إلكتروني</t>
+        </is>
+      </c>
+      <c r="E78" s="14" t="inlineStr">
+        <is>
+          <t>أولوية</t>
+        </is>
+      </c>
+      <c r="F78" s="14" t="inlineStr">
+        <is>
+          <t>أولوية</t>
+        </is>
+      </c>
+      <c r="G78" s="14" t="inlineStr">
+        <is>
+          <t>مدير حساب</t>
+        </is>
+      </c>
+      <c r="H78" s="15" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="I78" s="16" t="inlineStr">
+        <is>
+          <t>⚠️ جزئي</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="26" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>الربط والدعم</t>
+        </is>
+      </c>
+      <c r="B79" s="12" t="inlineStr">
+        <is>
           <t>اتفاقية مستوى خدمة (SLA)</t>
         </is>
       </c>
-      <c r="C78" s="13" t="inlineStr">
+      <c r="C79" s="13" t="inlineStr">
         <is>
           <t>التزام تعاقدي بزمن الرد ونسبة التشغيل</t>
         </is>
       </c>
-      <c r="D78" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="19" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H78" s="15" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="I78" s="17" t="inlineStr">
+      <c r="D79" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="19" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H79" s="15" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="I79" s="17" t="inlineStr">
         <is>
           <t>❌ غير منفّذ</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="30" customHeight="1">
-      <c r="A79" s="3" t="inlineStr">
+    <row r="80" ht="30" customHeight="1">
+      <c r="A80" s="3" t="inlineStr">
         <is>
           <t>الإجمالي</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="B80" s="3" t="inlineStr">
         <is>
           <t>المشمول في كل باقة</t>
         </is>
       </c>
-      <c r="C79" s="3">
-        <f>COUNTIF(H5:H78,"✔")&amp;" صفاً تظهر على الموقع"</f>
+      <c r="C80" s="3">
+        <f>COUNTIF(H5:H79,"✔")&amp;" صفاً تظهر على الموقع"</f>
         <v/>
       </c>
-      <c r="D79" s="3">
-        <f>COUNTIF(D5:D78,"✔")</f>
+      <c r="D80" s="3">
+        <f>COUNTIF(D5:D79,"✔")</f>
         <v/>
       </c>
-      <c r="E79" s="3">
-        <f>COUNTIF(E5:E78,"✔")</f>
+      <c r="E80" s="3">
+        <f>COUNTIF(E5:E79,"✔")</f>
         <v/>
       </c>
-      <c r="F79" s="3">
-        <f>COUNTIF(F5:F78,"✔")</f>
+      <c r="F80" s="3">
+        <f>COUNTIF(F5:F79,"✔")</f>
         <v/>
       </c>
-      <c r="G79" s="3">
-        <f>COUNTIF(G5:G78,"✔")</f>
+      <c r="G80" s="3">
+        <f>COUNTIF(G5:G79,"✔")</f>
         <v/>
       </c>
-      <c r="H79" s="3">
-        <f>COUNTIF(H5:H78,"✔")</f>
+      <c r="H80" s="3">
+        <f>COUNTIF(H5:H79,"✔")</f>
         <v/>
       </c>
-      <c r="I79" s="3">
-        <f>COUNTIF(I5:I78,"✅ منفّذ")&amp;" / "&amp;COUNTIF(I5:I78,"⚠️ جزئي")&amp;" / "&amp;COUNTIF(I5:I78,"❌ غير منفّذ")</f>
+      <c r="I80" s="3">
+        <f>COUNTIF(I5:I79,"✅ منفّذ")&amp;" / "&amp;COUNTIF(I5:I79,"⚠️ جزئي")&amp;" / "&amp;COUNTIF(I5:I79,"❌ غير منفّذ")</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A29:I29"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A63:I63"/>
     <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A75:I75"/>
-    <mergeCell ref="A44:I44"/>
+    <mergeCell ref="A76:I76"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A53:I53"/>
+    <mergeCell ref="A45:I45"/>
+    <mergeCell ref="A70:I70"/>
     <mergeCell ref="A22:I22"/>
-    <mergeCell ref="A69:I69"/>
     <mergeCell ref="A12:I12"/>
-    <mergeCell ref="A62:I62"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A54:I54"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4762,7 +4809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5078,12 +5125,32 @@
       </c>
       <c r="C18" s="26" t="inlineStr">
         <is>
-          <t>الرسائل الصوتية · تعديل الرسالة خلال 30 دقيقة · فهرسة دورات المحادثة · حالة متاح ومشغول · تصدير التقارير.</t>
+          <t>تطبيق الموظفين على الجوال (منشور على qhub-employee) · الرسائل الصوتية · تعديل الرسالة خلال 30 دقيقة · فهرسة دورات المحادثة · حالة متاح ومشغول · تصدير التقارير.</t>
         </is>
       </c>
       <c r="D18" s="27" t="inlineStr">
         <is>
-          <t>أُضيفت للمصفوفة. يستحق بعضها الظهور على الموقع — قرار تسويقي.</t>
+          <t>أُضيفت للمصفوفة. التطبيق أهمها: مبني ومنشور ولا ذكر له على صفحة الأسعار، بينما respond.io تعرضه على كل باقاتها.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="56" customHeight="1">
+      <c r="A19" s="28" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="25" t="inlineStr">
+        <is>
+          <t>ملاحظة على نطاق هذا التدقيق</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="inlineStr">
+        <is>
+          <t>التدقيق قرأ ريبو اللوحة (chatly) وريبو الموقع (qhub-landing). تطبيق الموظفين في ريبو ثالث، فغاب عن أول نسختين من هذا الملف حتى نُبِّهتُ إليه.</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="inlineStr">
+        <is>
+          <t>إن كانت هناك ريبوهات أخرى في المنتج — لوحة أدمن منفصلة، أو باكند — فقد تحمل مزايا مصنّفة هنا «غير منفّذة».</t>
         </is>
       </c>
     </row>
@@ -5520,14 +5587,14 @@
           <t>تطبيق على كل الباقات بما فيها Starter</t>
         </is>
       </c>
-      <c r="D18" s="30" t="inlineStr">
-        <is>
-          <t>غير موجود</t>
+      <c r="D18" s="31" t="inlineStr">
+        <is>
+          <t>تطبيق موظفين مبني ومنشور على qhub-employee</t>
         </is>
       </c>
       <c r="E18" s="27" t="inlineStr">
         <is>
-          <t>معروض في ملفك على ثلاث باقات ولا أثر له — إما يُبنى أو يُشطب.</t>
+          <t>موجود عندنا وغير معروض على صفحة الأسعار — فرصة ضائعة. respond.io تعرضه على كل باقة بما فيها الأرخص.</t>
         </is>
       </c>
     </row>

--- a/docs/Qhub - مصفوفة الباقات والمزايا.xlsx
+++ b/docs/Qhub - مصفوفة الباقات والمزايا.xlsx
@@ -170,7 +170,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -192,11 +192,55 @@
         <color rgb="00CBD5E1"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -291,6 +335,8 @@
     <xf numFmtId="0" fontId="14" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -719,6 +765,11 @@
           <t>الهوية</t>
         </is>
       </c>
+      <c r="B5" s="32" t="n"/>
+      <c r="C5" s="32" t="n"/>
+      <c r="D5" s="32" t="n"/>
+      <c r="E5" s="32" t="n"/>
+      <c r="F5" s="33" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
@@ -886,6 +937,11 @@
           <t>السعر</t>
         </is>
       </c>
+      <c r="B11" s="32" t="n"/>
+      <c r="C11" s="32" t="n"/>
+      <c r="D11" s="32" t="n"/>
+      <c r="E11" s="32" t="n"/>
+      <c r="F11" s="33" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
@@ -948,6 +1004,11 @@
           <t>الحدود المعتمدة</t>
         </is>
       </c>
+      <c r="B14" s="32" t="n"/>
+      <c r="C14" s="32" t="n"/>
+      <c r="D14" s="32" t="n"/>
+      <c r="E14" s="32" t="n"/>
+      <c r="F14" s="33" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
@@ -1093,6 +1154,11 @@
           <t>الحدود أعلاه تُعرَض للعميل فقط — لا يوجد في الكود ما يمنع تجاوزها. راجع ورقة «النواقص»، البند 1.</t>
         </is>
       </c>
+      <c r="B21" s="32" t="n"/>
+      <c r="C21" s="32" t="n"/>
+      <c r="D21" s="32" t="n"/>
+      <c r="E21" s="32" t="n"/>
+      <c r="F21" s="33" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1194,6 +1260,14 @@
           <t>الأساسيات</t>
         </is>
       </c>
+      <c r="B5" s="32" t="n"/>
+      <c r="C5" s="32" t="n"/>
+      <c r="D5" s="32" t="n"/>
+      <c r="E5" s="32" t="n"/>
+      <c r="F5" s="32" t="n"/>
+      <c r="G5" s="32" t="n"/>
+      <c r="H5" s="32" t="n"/>
+      <c r="I5" s="33" t="n"/>
     </row>
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
@@ -1297,27 +1371,27 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>عدد الحسابات المربوطة</t>
+          <t>عدد الحسابات في كل قناة</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>كم حساباً فعلياً تربط — رقمَي واتساب مثلاً حسابان لا قناة واحدة</t>
+          <t>الحدّ محسوب لكل قناة على حدة لا على المجموع — على الاحترافية مثلاً: رقمَا واتساب وصفحتا فيسبوك وصندوقا بريد</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>حساب واحد</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>حسابان</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5 حسابات</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -1483,6 +1557,14 @@
           <t>القنوات</t>
         </is>
       </c>
+      <c r="B12" s="32" t="n"/>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="32" t="n"/>
+      <c r="E12" s="32" t="n"/>
+      <c r="F12" s="32" t="n"/>
+      <c r="G12" s="32" t="n"/>
+      <c r="H12" s="32" t="n"/>
+      <c r="I12" s="33" t="n"/>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
@@ -1913,6 +1995,14 @@
           <t>صندوق الوارد</t>
         </is>
       </c>
+      <c r="B22" s="32" t="n"/>
+      <c r="C22" s="32" t="n"/>
+      <c r="D22" s="32" t="n"/>
+      <c r="E22" s="32" t="n"/>
+      <c r="F22" s="32" t="n"/>
+      <c r="G22" s="32" t="n"/>
+      <c r="H22" s="32" t="n"/>
+      <c r="I22" s="33" t="n"/>
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
@@ -2249,6 +2339,14 @@
           <t>المساعد الذكي</t>
         </is>
       </c>
+      <c r="B30" s="32" t="n"/>
+      <c r="C30" s="32" t="n"/>
+      <c r="D30" s="32" t="n"/>
+      <c r="E30" s="32" t="n"/>
+      <c r="F30" s="32" t="n"/>
+      <c r="G30" s="32" t="n"/>
+      <c r="H30" s="32" t="n"/>
+      <c r="I30" s="33" t="n"/>
     </row>
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
@@ -2914,6 +3012,14 @@
           <t>التسويق والحملات</t>
         </is>
       </c>
+      <c r="B45" s="32" t="n"/>
+      <c r="C45" s="32" t="n"/>
+      <c r="D45" s="32" t="n"/>
+      <c r="E45" s="32" t="n"/>
+      <c r="F45" s="32" t="n"/>
+      <c r="G45" s="32" t="n"/>
+      <c r="H45" s="32" t="n"/>
+      <c r="I45" s="33" t="n"/>
     </row>
     <row r="46" ht="26" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
@@ -3297,6 +3403,14 @@
           <t>الفريق والصلاحيات</t>
         </is>
       </c>
+      <c r="B54" s="32" t="n"/>
+      <c r="C54" s="32" t="n"/>
+      <c r="D54" s="32" t="n"/>
+      <c r="E54" s="32" t="n"/>
+      <c r="F54" s="32" t="n"/>
+      <c r="G54" s="32" t="n"/>
+      <c r="H54" s="32" t="n"/>
+      <c r="I54" s="33" t="n"/>
     </row>
     <row r="55" ht="26" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
@@ -3680,6 +3794,14 @@
           <t>العملاء</t>
         </is>
       </c>
+      <c r="B63" s="32" t="n"/>
+      <c r="C63" s="32" t="n"/>
+      <c r="D63" s="32" t="n"/>
+      <c r="E63" s="32" t="n"/>
+      <c r="F63" s="32" t="n"/>
+      <c r="G63" s="32" t="n"/>
+      <c r="H63" s="32" t="n"/>
+      <c r="I63" s="33" t="n"/>
     </row>
     <row r="64" ht="26" customHeight="1">
       <c r="A64" s="6" t="inlineStr">
@@ -3969,6 +4091,14 @@
           <t>التقارير</t>
         </is>
       </c>
+      <c r="B70" s="32" t="n"/>
+      <c r="C70" s="32" t="n"/>
+      <c r="D70" s="32" t="n"/>
+      <c r="E70" s="32" t="n"/>
+      <c r="F70" s="32" t="n"/>
+      <c r="G70" s="32" t="n"/>
+      <c r="H70" s="32" t="n"/>
+      <c r="I70" s="33" t="n"/>
     </row>
     <row r="71" ht="26" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
@@ -4211,6 +4341,14 @@
           <t>الربط والدعم</t>
         </is>
       </c>
+      <c r="B76" s="32" t="n"/>
+      <c r="C76" s="32" t="n"/>
+      <c r="D76" s="32" t="n"/>
+      <c r="E76" s="32" t="n"/>
+      <c r="F76" s="32" t="n"/>
+      <c r="G76" s="32" t="n"/>
+      <c r="H76" s="32" t="n"/>
+      <c r="I76" s="33" t="n"/>
     </row>
     <row r="77" ht="26" customHeight="1">
       <c r="A77" s="6" t="inlineStr">
@@ -4733,7 +4871,7 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>عدد الحسابات المربوطة</t>
+          <t>عدد الحسابات في كل قناة</t>
         </is>
       </c>
       <c r="B13" s="22" t="inlineStr">
@@ -4743,7 +4881,7 @@
       </c>
       <c r="C13" s="22" t="inlineStr">
         <is>
-          <t>1 / 2 / 5 / —</t>
+          <t>1 / 2 / 5 / — (بلا تحديد: إجمالي أم لكل قناة)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -4753,12 +4891,12 @@
       </c>
       <c r="E13" s="21" t="inlineStr">
         <is>
-          <t>1 / 2 / 5 / بلا حد</t>
+          <t>1 / 2 / 5 / بلا حد — لكل قناة</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t>إضافة limits.accounts للنوع Plan، وإضافة الصف لجدول الموقع. حدّ مستقل عن القنوات: رقمَا واتساب = قناة واحدة وحسابان.</t>
+          <t>إضافة limits.accountsPerChannel للنوع Plan، وإضافة الصف لجدول الموقع. حدّ مستقل عن القنوات ويُطبَّق داخل كل نوع: القنوات تحدّد كم نوعاً تفتح، وهذا يحدّد كم حساباً داخل النوع الواحد.</t>
         </is>
       </c>
     </row>
@@ -4900,17 +5038,17 @@
       </c>
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>عدد الحسابات المربوطة بلا حقل</t>
+          <t>حدّ الحسابات لكل قناة بلا حقل</t>
         </is>
       </c>
       <c r="C7" s="26" t="inlineStr">
         <is>
-          <t>حدّ مطلوب ومتّفق عليه، والنوع Plan ما فيه limits.accounts. القنوات في النظام صفوف مستقلة من نوع Channel، فربط رقمَي واتساب يُنشئ سجلّين تحت نوع واحد — أي أن التمييز بين «القناة» و«الحساب» قائم في البيانات وينقصه الحدّ فقط.</t>
+          <t>حدّ مطلوب ومتّفق عليه، والنوع Plan ما فيه حقل له. القنوات في النظام صفوف مستقلة من نوع Channel لكل منها type، فربط رقمَي واتساب يُنشئ سجلّين تحت النوع نفسه — أي أن التمييز بين «نوع القناة» و«الحساب» قائم في البيانات وينقصه الحدّ فقط.</t>
         </is>
       </c>
       <c r="D7" s="27" t="inlineStr">
         <is>
-          <t>إضافة limits.accounts للنوع وللباقات الأربع. أقرب حدّ للتنفيذ لأن البيانات جاهزة — يكفي عدّ سجلات Channel.</t>
+          <t>إضافة limits.accountsPerChannel للنوع وللباقات الأربع، والفحص عند addChannel بعدّ channels.filter(c =&gt; c.type === type). أقرب حدّ للتنفيذ لأن البيانات جاهزة.</t>
         </is>
       </c>
     </row>
@@ -5631,6 +5769,10 @@
           <t>أسعارهم للمقارنة — BEON: من 1,199 ج.م إلى 12,399 ج.م شهرياً · respond.io: Starter 79$ · Growth 159$ · Advanced 279–349$ · نحن: 19$ إلى 249$</t>
         </is>
       </c>
+      <c r="B21" s="32" t="n"/>
+      <c r="C21" s="32" t="n"/>
+      <c r="D21" s="32" t="n"/>
+      <c r="E21" s="33" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
